--- a/src/attributions/attributions_saliency_traj_75.xlsx
+++ b/src/attributions/attributions_saliency_traj_75.xlsx
@@ -1568,1140 +1568,1140 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008786200545728207</v>
+        <v>0.0004627090529538691</v>
       </c>
       <c r="B3" t="n">
-        <v>0.05096505582332611</v>
+        <v>0.0069999392144382</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001882541459053755</v>
+        <v>0.002339473459869623</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01330121140927076</v>
+        <v>0.0003121152985841036</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002011090982705355</v>
+        <v>0.002097527030855417</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0191690307110548</v>
+        <v>0.00638931430876255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001535534858703613</v>
+        <v>0.001180823310278356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001275809016078711</v>
+        <v>0.0008547015022486448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006634311284869909</v>
+        <v>0.003144015092402697</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007709547411650419</v>
+        <v>0.001518103526905179</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03381180018186569</v>
+        <v>0.009431302547454834</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007499201223254204</v>
+        <v>0.002531331963837147</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01318413577973843</v>
+        <v>0.002122978679835796</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01378658972680569</v>
+        <v>0.001931645441800356</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02478310652077198</v>
+        <v>0.005727873183786869</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004805419594049454</v>
+        <v>8.473794150631875e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01206333376467228</v>
+        <v>0.002201046561822295</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004330466501414776</v>
+        <v>0.00304301711730659</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001531859976239502</v>
+        <v>0.0003222974482923746</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00696639996021986</v>
+        <v>0.001767862588167191</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002298319479450583</v>
+        <v>0.0002613802498672158</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008461076766252518</v>
+        <v>0.0006983602652326226</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004887946415692568</v>
+        <v>0.001205142587423325</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006948588881641626</v>
+        <v>0.0006016106344759464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002648925641551614</v>
+        <v>0.0008287580567412078</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005849966313689947</v>
+        <v>7.16320937499404e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004116359166800976</v>
+        <v>0.0005711862468160689</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001051960978657007</v>
+        <v>9.205116657540202e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.00522463908419013</v>
+        <v>8.87580681592226e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.005833302158862352</v>
+        <v>0.000871025025844574</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.005895011592656374</v>
+        <v>0.0007754045072942972</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.007419382221996784</v>
+        <v>0.00428425008431077</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.002166455378755927</v>
+        <v>0.0001069440040737391</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.007430267054587603</v>
+        <v>0.000852731172926724</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0008280817419290543</v>
+        <v>0.001922600087709725</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.00525376945734024</v>
+        <v>7.978167559485883e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.006029710173606873</v>
+        <v>0.0003518659505061805</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.009871506132185459</v>
+        <v>0.001776966266334057</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0003761400294024497</v>
+        <v>0.0001908328558783978</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.00642872229218483</v>
+        <v>0.0003387109900359064</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001590193947777152</v>
+        <v>0.001595130423083901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.006550751626491547</v>
+        <v>0.0009213667362928391</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0009867380140349269</v>
+        <v>0.000423759629484266</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001510670175775886</v>
+        <v>0.001391676836647093</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0009171924320980906</v>
+        <v>0.0005301728961057961</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.004920818377286196</v>
+        <v>0.0001294514804612845</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.03337089717388153</v>
+        <v>0.007425563409924507</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.001400903332978487</v>
+        <v>0.001328407786786556</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.006936794146895409</v>
+        <v>0.0004901716019958258</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.009883463382720947</v>
+        <v>0.001071145059540868</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.00437765009701252</v>
+        <v>0.002087948843836784</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.006723836529999971</v>
+        <v>0.00074366619810462</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.001297033624723554</v>
+        <v>0.001075023668818176</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.003655718639492989</v>
+        <v>0.0007465914823114872</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.004922598134726286</v>
+        <v>7.46489386074245e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01037974562495947</v>
+        <v>0.002293176483362913</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.002800511894747615</v>
+        <v>0.0005132525693625212</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0003316202200949192</v>
+        <v>0.0003948452649638057</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01778968423604965</v>
+        <v>0.002960650715976954</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.006818256340920925</v>
+        <v>0.001379075460135937</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.007932744920253754</v>
+        <v>0.0007507861009798944</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.009272905997931957</v>
+        <v>0.0004996970528736711</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.002176554873585701</v>
+        <v>0.001576970447786152</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0101962061598897</v>
+        <v>0.0006269903969950974</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001377366832457483</v>
+        <v>6.566861702594906e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.00166369485668838</v>
+        <v>0.0001464725937694311</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0002135832328349352</v>
+        <v>0.0009198924526572227</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.004297298844903708</v>
+        <v>0.001432890072464943</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0004707864718511701</v>
+        <v>0.00135862804017961</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.004372323397547007</v>
+        <v>0.0006708728615194559</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002248206175863743</v>
+        <v>0.0002165667829103768</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.001285257283598185</v>
+        <v>0.0009484832407906651</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.004887099377810955</v>
+        <v>0.001295615220442414</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01638380251824856</v>
+        <v>0.005201573483645916</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.001762214815244079</v>
+        <v>0.0006219246424734592</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.004285705275833607</v>
+        <v>0.00114265107549727</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.002619369421154261</v>
+        <v>0.001425446709617972</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0116158127784729</v>
+        <v>0.001196498982608318</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.001821366022340953</v>
+        <v>0.0004428061656653881</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.00292150629684329</v>
+        <v>0.0011379070347175</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002017059363424778</v>
+        <v>0.000785930547863245</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.004716323688626289</v>
+        <v>0.000362424150807783</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.007354429457336664</v>
+        <v>0.001652593724429607</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0009648378472775221</v>
+        <v>8.206548227462918e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0007056257454678416</v>
+        <v>0.0003187296679243445</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.002633085008710623</v>
+        <v>0.001333192805759609</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.003419505665078759</v>
+        <v>0.0009866415057331324</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0041492716409266</v>
+        <v>5.125335155753419e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0008895847131498158</v>
+        <v>0.0006962822517380118</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.001267395680770278</v>
+        <v>0.0003632844018284231</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0001732953533064574</v>
+        <v>0.001085177413187921</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0004574214108288288</v>
+        <v>0.0006053072866052389</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.003948253113776445</v>
+        <v>0.001457586651667953</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.006511902436614037</v>
+        <v>0.0002858398365788162</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.002892318880185485</v>
+        <v>0.0006675691693089902</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.009059244766831398</v>
+        <v>0.001397988176904619</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.009785604663193226</v>
+        <v>9.12813120521605e-05</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.01148424856364727</v>
+        <v>0.0006754633504897356</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.007004437502473593</v>
+        <v>0.0007906657992862165</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.003858934156596661</v>
+        <v>0.0002168904757127166</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.006395929958671331</v>
+        <v>0.00162190617993474</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0005183059256523848</v>
+        <v>1.391541445627809e-06</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.002510184654965997</v>
+        <v>0.0001337642315775156</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.003530092304572463</v>
+        <v>0.0004863156354986131</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.00609627366065979</v>
+        <v>0.001172559568658471</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.004359765443950891</v>
+        <v>0.000351478869561106</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.001275560818612576</v>
+        <v>0.0007013115100562572</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.000411947607062757</v>
+        <v>0.0004467359103728086</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.004527626559138298</v>
+        <v>0.001103725051507354</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.006041594780981541</v>
+        <v>0.001601979252882302</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.001535735907964408</v>
+        <v>0.0009731174213811755</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.002437429968267679</v>
+        <v>0.0006973242852836847</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.001718686195090413</v>
+        <v>0.001733524492010474</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.003741302527487278</v>
+        <v>0.004656605888158083</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.006213280837982893</v>
+        <v>0.0003095362044405192</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.006837798748165369</v>
+        <v>0.002099962905049324</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.002760800998657942</v>
+        <v>0.001474363729357719</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.005465247668325901</v>
+        <v>7.652054773643613e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.0003852601512335241</v>
+        <v>0.001010950771160424</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.001325006829574704</v>
+        <v>0.000681354955304414</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.01163400989025831</v>
+        <v>0.0009807546157389879</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.00611294386908412</v>
+        <v>1.889175109681673e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.007059856783598661</v>
+        <v>0.0003391770296730101</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0003893341054208577</v>
+        <v>0.0005202304455451667</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.0001049165148288012</v>
+        <v>0.0001252986257895827</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.002944285282865167</v>
+        <v>0.0002650849055498838</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.004382107872515917</v>
+        <v>0.0008839110378175974</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.003196085104718804</v>
+        <v>0.0003525255597196519</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.01047846674919128</v>
+        <v>0.001076809363439679</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.003125671297311783</v>
+        <v>0.0004352856776677072</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.006590666715055704</v>
+        <v>0.000617520825471729</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.003058610716834664</v>
+        <v>0.001069416292011738</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.002390187466517091</v>
+        <v>0.000177549067302607</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.008645439520478249</v>
+        <v>0.0003768784808926284</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.007150216493755579</v>
+        <v>0.002626096364110708</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0004281657747924328</v>
+        <v>0.0002033608761848882</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.002620561746880412</v>
+        <v>0.0005505546578206122</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.00140293431468308</v>
+        <v>0.0008723096107132733</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.01013072859495878</v>
+        <v>0.001116256811656058</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.005975713487714529</v>
+        <v>0.001170826843008399</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.003446729620918632</v>
+        <v>0.0008853448089212179</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.007608162239193916</v>
+        <v>0.0002265590592287481</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.001246921601705253</v>
+        <v>0.0001071794977178797</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.002816777909174562</v>
+        <v>0.001115996739827096</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0009261196246370673</v>
+        <v>0.0002087021712213755</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.004896021913737059</v>
+        <v>0.001138966297730803</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.003522002371028066</v>
+        <v>0.0004413769347593188</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.002010360825806856</v>
+        <v>0.001049846992827952</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.002012924756854773</v>
+        <v>0.002836217172443867</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01966438442468643</v>
+        <v>0.002486764453351498</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.002866771072149277</v>
+        <v>0.0004705573082901537</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.003249566769227386</v>
+        <v>0.0001294698449783027</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.004394488874822855</v>
+        <v>0.0006014943355694413</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.004049431532621384</v>
+        <v>0.0001340065646218136</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.006660324521362782</v>
+        <v>0.001840111566707492</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.001583213917911053</v>
+        <v>0.0001312164240516722</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0007844628999009728</v>
+        <v>0.0003135424922220409</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.003683065064251423</v>
+        <v>0.001183608314022422</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.005607206374406815</v>
+        <v>0.000887213391251862</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.00312836654484272</v>
+        <v>0.0002471820334903896</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.0001287271152250469</v>
+        <v>0.0002589707728475332</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.001014292938634753</v>
+        <v>0.0006641540676355362</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.002490748185664415</v>
+        <v>0.000495719606988132</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.007829926908016205</v>
+        <v>0.002030253876000643</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.003028165549039841</v>
+        <v>0.001580669777467847</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.01004775799810886</v>
+        <v>0.000837376166600734</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.008163400925695896</v>
+        <v>0.0006078177830204368</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.00924135185778141</v>
+        <v>0.000755304703488946</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.0008873115293681622</v>
+        <v>0.000177407287992537</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.007227583322674036</v>
+        <v>0.002234206302091479</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.008369420655071735</v>
+        <v>0.002021766267716885</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.0008938164683058858</v>
+        <v>9.711866732686758e-05</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.000916670891456306</v>
+        <v>0.001405130606144667</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.008977894671261311</v>
+        <v>0.0003377171233296394</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.001415914390236139</v>
+        <v>0.003407878102734685</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01361969113349915</v>
+        <v>0.003022389486432076</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.008277011103928089</v>
+        <v>0.001964897615835071</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.006652169860899448</v>
+        <v>0.001861878205090761</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.003089184872806072</v>
+        <v>0.004126030951738358</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0001936968183144927</v>
+        <v>0.002286615548655391</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.0005784569075331092</v>
+        <v>0.002076494041830301</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.005599895026534796</v>
+        <v>0.0005298972828313708</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.001067324192263186</v>
+        <v>0.0003719998348969966</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.003512104041874409</v>
+        <v>0.0006960969185456634</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.002433954738080502</v>
+        <v>1.729489304125309e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.001264062011614442</v>
+        <v>0.0003756998339667916</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.005554705392569304</v>
+        <v>0.0002295047015650198</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.0007601546822115779</v>
+        <v>0.0001991678436752409</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.002828037831932306</v>
+        <v>0.001203150954097509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.004326048772782087</v>
+        <v>0.000341896346071735</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04588586464524269</v>
+        <v>0.008031412959098816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002235371852293611</v>
+        <v>0.0001282829325646162</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02581699565052986</v>
+        <v>0.008352566510438919</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008989805355668068</v>
+        <v>0.002181313000619411</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0114672128111124</v>
+        <v>0.00154978025238961</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004643128719180822</v>
+        <v>0.004404780454933643</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006799532100558281</v>
+        <v>0.003855250077322125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001139899017289281</v>
+        <v>0.0007662692805752158</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008302351459860802</v>
+        <v>4.819878085982054e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03463602066040039</v>
+        <v>0.008518009446561337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00107538967859</v>
+        <v>0.001131802913732827</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02204939723014832</v>
+        <v>0.01178006082773209</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01178620848804712</v>
+        <v>0.003979355562478304</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01765616238117218</v>
+        <v>0.001188708934932947</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003231420880183578</v>
+        <v>0.00425339862704277</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001539836870506406</v>
+        <v>0.0007352082757279277</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00597356865182519</v>
+        <v>0.001167061505839229</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002184184500947595</v>
+        <v>1.364812487736344e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005641472060233355</v>
+        <v>0.0004180985270068049</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005155724007636309</v>
+        <v>1.647242606850341e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006255543790757656</v>
+        <v>0.0001814709976315498</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002015113364905119</v>
+        <v>0.002130207838490605</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002767334692180157</v>
+        <v>0.002081281738355756</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006936084479093552</v>
+        <v>0.0004106705018784851</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004394527524709702</v>
+        <v>0.001874248497188091</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003806289518252015</v>
+        <v>0.002588443458080292</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001797421835362911</v>
+        <v>0.0008844326948747039</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005944856442511082</v>
+        <v>0.0006082718027755618</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0006334219360724092</v>
+        <v>0.0005650458624586463</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002478378359228373</v>
+        <v>0.001132335048168898</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004093112424015999</v>
+        <v>0.0001131645985879004</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002307923743501306</v>
+        <v>0.002685235580429435</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001041476614773273</v>
+        <v>0.0001959765213541687</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001078561297617853</v>
+        <v>0.001022576470859349</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004716284573078156</v>
+        <v>0.0007095637265592813</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.004343819804489613</v>
+        <v>0.0001713453675620258</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.007593864109367132</v>
+        <v>0.001197409466840327</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002778121503069997</v>
+        <v>0.0009479227592237294</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002573034726083279</v>
+        <v>0.001709452364593744</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002953008515760303</v>
+        <v>0.0002199436421506107</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.004303701221942902</v>
+        <v>0.002017811872065067</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001183779095299542</v>
+        <v>0.001619316870346665</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003205565037205815</v>
+        <v>0.0004688574408646673</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.004852131474763155</v>
+        <v>0.0005203799810260534</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.006547924131155014</v>
+        <v>1.482386142015457e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.03103922307491302</v>
+        <v>0.004664447624236345</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001257541589438915</v>
+        <v>0.0008834546897560358</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.008235624060034752</v>
+        <v>0.00455250171944499</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.002263382542878389</v>
+        <v>0.007273594383150339</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001777645200490952</v>
+        <v>0.0009844421874731779</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0009109304519370198</v>
+        <v>0.0001265756436623633</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.002589433453977108</v>
+        <v>0.0008747113170102239</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006963666994124651</v>
+        <v>0.0002865050919353962</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.003147943876683712</v>
+        <v>0.001029508071951568</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.004453752655535936</v>
+        <v>0.0005442083347588778</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.006360891275107861</v>
+        <v>0.001504817162640393</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.002198715694248676</v>
+        <v>0.001148676732555032</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.01514136604964733</v>
+        <v>0.004091169219464064</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.002204051706939936</v>
+        <v>0.0004674504743888974</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.007549438625574112</v>
+        <v>0.001166260452009737</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004633234348148108</v>
+        <v>0.004406068474054337</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001252005924470723</v>
+        <v>0.0003318967064842582</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.004916644655168056</v>
+        <v>4.152843030169606e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0002242594928247854</v>
+        <v>0.001042788266204298</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001074580824933946</v>
+        <v>0.000250342272920534</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.00465740030631423</v>
+        <v>0.001700931461527944</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0007952555897645652</v>
+        <v>0.0007104146061465144</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0008505336008965969</v>
+        <v>0.000180865652509965</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00221532117575407</v>
+        <v>3.057811409235001e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001081476453691721</v>
+        <v>0.001732397824525833</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.003735349280759692</v>
+        <v>0.0004382433835417032</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.00427577830851078</v>
+        <v>0.0003448449133429676</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01737469993531704</v>
+        <v>0.002661361359059811</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.003398976055905223</v>
+        <v>0.0008657185244373977</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.005822126753628254</v>
+        <v>0.003760641207918525</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.280627662315965e-05</v>
+        <v>0.003047286532819271</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003874956630170345</v>
+        <v>0.002242194022983313</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.002709978492930532</v>
+        <v>0.001150322612375021</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001024740748107433</v>
+        <v>0.0009743532864376903</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.005596850533038378</v>
+        <v>0.001827452797442675</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002710221335291862</v>
+        <v>0.0002423234691377729</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.007650014013051987</v>
+        <v>0.00219721719622612</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003907828126102686</v>
+        <v>0.0003841058351099491</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002894583623856306</v>
+        <v>0.003199369879439473</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0009857119293883443</v>
+        <v>0.0003777822712436318</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003073368454352021</v>
+        <v>0.0002420060336589813</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.002098542172461748</v>
+        <v>0.0002779316273517907</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0001976685598492622</v>
+        <v>3.574314177967608e-06</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.003403858048841357</v>
+        <v>0.0006251659942790866</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.004978238604962826</v>
+        <v>0.0004176172951702029</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0004243415896780789</v>
+        <v>0.002180334646254778</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.003697580192238092</v>
+        <v>0.003324747551232576</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.006065290421247482</v>
+        <v>0.004469479899853468</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004239308647811413</v>
+        <v>0.0005120168207213283</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003552284790202975</v>
+        <v>0.001943163690157235</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.00618482381105423</v>
+        <v>0.0008820684161037207</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.01124671846628189</v>
+        <v>0.001711276010610163</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0017369429115206</v>
+        <v>0.001733198296278715</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.002385082421824336</v>
+        <v>0.0001179327955469489</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.006785090081393719</v>
+        <v>0.00215943856164813</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.00409106258302927</v>
+        <v>0.0004690634086728096</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.005804404616355896</v>
+        <v>0.003498260397464037</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003324461576994509</v>
+        <v>0.000611183000728488</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.002990552224218845</v>
+        <v>0.0003317859664093703</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001989684998989105</v>
+        <v>0.0004541318339761347</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0007548036519438028</v>
+        <v>0.0003274621849413961</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.002148859668523073</v>
+        <v>0.0009139657486230135</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.003640533424913883</v>
+        <v>0.0005636558053083718</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.005158227868378162</v>
+        <v>0.001007324899546802</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.928318619728088e-05</v>
+        <v>0.0004673638322856277</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.01391483470797539</v>
+        <v>0.002340627601370215</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.007592982612550259</v>
+        <v>7.97085085650906e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003748664865270257</v>
+        <v>0.001171574695035815</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.008824423886835575</v>
+        <v>0.001418754924088717</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0006560366600751877</v>
+        <v>0.004180774092674255</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.002165603451430798</v>
+        <v>0.0004335364501457661</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.005979747977107763</v>
+        <v>8.172739762812853e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.003812231589108706</v>
+        <v>0.0009372380445711315</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0001084150280803442</v>
+        <v>0.0008291043341159821</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001440369989722967</v>
+        <v>0.001143785077147186</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.004874043166637421</v>
+        <v>0.0007894174195826054</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001711620832793415</v>
+        <v>0.001391121651977301</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001042337738908827</v>
+        <v>0.001654034829698503</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001470115035772324</v>
+        <v>0.001658856635913253</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.00699614267796278</v>
+        <v>0.004182515200227499</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.002618007594719529</v>
+        <v>0.000114777561975643</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0008833631873130798</v>
+        <v>0.0002456014917697757</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.01144557073712349</v>
+        <v>0.0005693995044566691</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0008026349823921919</v>
+        <v>0.0008819864597171545</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.006653034593909979</v>
+        <v>0.0005691798869520426</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0009674380999058485</v>
+        <v>0.001162281958386302</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001084696734324098</v>
+        <v>0.0004108050197828561</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0001641431590542197</v>
+        <v>0.005015962291508913</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0005723890499211848</v>
+        <v>0.003551883157342672</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.00219225394539535</v>
+        <v>0.0007606954895891249</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.004722834564745426</v>
+        <v>0.001452985219657421</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.002031505107879639</v>
+        <v>0.0007920342031866312</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.003323489334434271</v>
+        <v>0.003482223954051733</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.00282976939342916</v>
+        <v>0.0001307975617237389</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001149620045907795</v>
+        <v>0.001050947699695826</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.002035826677456498</v>
+        <v>9.377102833241224e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.00215771165676415</v>
+        <v>0.0003207148401997983</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.00064292480237782</v>
+        <v>0.001108404132537544</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.001774827018380165</v>
+        <v>0.001107351039536297</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.004146608989685774</v>
+        <v>0.00236416351981461</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.003120702691376209</v>
+        <v>0.0003675587940961123</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.00688549317419529</v>
+        <v>0.002177959075197577</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.003455298254266381</v>
+        <v>0.001176249352283776</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01295668818056583</v>
+        <v>0.001180189661681652</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.004046590998768806</v>
+        <v>0.001252189977094531</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.005377890076488256</v>
+        <v>0.0006209880812093616</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.003759447718039155</v>
+        <v>0.002420649165287614</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.00214856956154108</v>
+        <v>0.0003233476309105754</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.006179482210427523</v>
+        <v>0.002402374753728509</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.003189742099493742</v>
+        <v>0.0003772225172724575</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.004607896320521832</v>
+        <v>0.0036575214471668</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.001370148500427604</v>
+        <v>0.0005066394805908203</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.003168942406773567</v>
+        <v>0.0006021335138939321</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.003361370181664824</v>
+        <v>0.0005811852170154452</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0002927923342213035</v>
+        <v>5.675328429788351e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.00264609488658607</v>
+        <v>0.001047090976499021</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0005880799726583064</v>
+        <v>0.0002487684832885861</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.005545731633901596</v>
+        <v>0.00113384728319943</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.004897492006421089</v>
+        <v>0.001434615813195705</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.004002015106379986</v>
+        <v>0.002081043552607298</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.000284968817140907</v>
+        <v>0.0003093369014095515</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.001169955474324524</v>
+        <v>0.0005462879198603332</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.000650618108920753</v>
+        <v>0.0005401687230914831</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.003215119941160083</v>
+        <v>0.0009388795588165522</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.005063620395958424</v>
+        <v>0.001265298342332244</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.004542904905974865</v>
+        <v>0.0009533002157695591</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0003836361865978688</v>
+        <v>0.001339371432550251</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.005101622082293034</v>
+        <v>0.0002786681288853288</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.004381889943033457</v>
+        <v>0.00236302730627358</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.01098454743623734</v>
+        <v>0.0009678789647296071</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.001828259089961648</v>
+        <v>0.00171960040461272</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.002837635343894362</v>
+        <v>0.0002345384127693251</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.002650953596457839</v>
+        <v>0.002129218773916364</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.004760940093547106</v>
+        <v>0.002784099197015166</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.004001603927463293</v>
+        <v>0.0009474682155996561</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.002031031530350447</v>
+        <v>0.0006327972514554858</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.004545771516859531</v>
+        <v>0.0006523474585264921</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0007912101573310792</v>
+        <v>0.003178105223923922</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0101423179730773</v>
+        <v>0.00289773684926331</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.002586865797638893</v>
+        <v>0.0009102175245061517</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.01820886321365833</v>
+        <v>0.002796492306515574</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.00366936856880784</v>
+        <v>0.000240752415265888</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.004687448497861624</v>
+        <v>0.0003158199833706021</v>
       </c>
     </row>
     <row r="5">
@@ -3275,1709 +3275,1709 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.715764170739931e-07</v>
+        <v>8.353784886061533e-10</v>
       </c>
       <c r="B6" t="n">
-        <v>2.170964762626681e-06</v>
+        <v>3.262167203033073e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.777578972905758e-07</v>
+        <v>5.811020553636581e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>9.444385113965836e-07</v>
+        <v>2.120760650425879e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>4.769136197069201e-08</v>
+        <v>1.58657098570103e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.827729931846989e-07</v>
+        <v>1.358886059232844e-10</v>
       </c>
       <c r="G6" t="n">
-        <v>3.730194819695498e-09</v>
+        <v>3.120420588587081e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>2.939415999492212e-08</v>
+        <v>2.582905833659055e-10</v>
       </c>
       <c r="I6" t="n">
-        <v>3.157243355644823e-08</v>
+        <v>1.760480927703867e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>2.982013427299535e-07</v>
+        <v>2.363544360228786e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>1.43648253470019e-06</v>
+        <v>4.25754276278667e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.153574746837194e-08</v>
+        <v>9.573707382415364e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>9.499015050096205e-07</v>
+        <v>1.070272204195533e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.525366369354742e-07</v>
+        <v>2.274070487473523e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.684317218561773e-07</v>
+        <v>1.270214072812692e-10</v>
       </c>
       <c r="P6" t="n">
-        <v>1.019764468424e-07</v>
+        <v>6.592216772460802e-10</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.626769912694726e-07</v>
+        <v>1.477097777424774e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.072573141414068e-08</v>
+        <v>4.578980805636235e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>6.457707257823131e-09</v>
+        <v>9.870299022551876e-11</v>
       </c>
       <c r="T6" t="n">
-        <v>2.464947215230495e-07</v>
+        <v>2.758342165787298e-12</v>
       </c>
       <c r="U6" t="n">
-        <v>8.341644530673875e-08</v>
+        <v>7.990241107647122e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.86618777320291e-07</v>
+        <v>1.548395023309723e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>1.707711483334151e-08</v>
+        <v>4.870172598536726e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>2.435817236801086e-07</v>
+        <v>5.011573100954791e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.419311897483567e-07</v>
+        <v>8.812667262603213e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.989582849811995e-08</v>
+        <v>2.092142709075873e-10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.171430952240371e-07</v>
+        <v>6.278675357407337e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.505270526233289e-08</v>
+        <v>3.792936242863476e-10</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.50459294193206e-07</v>
+        <v>3.15899612024495e-10</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.272912417808584e-08</v>
+        <v>4.499201011753939e-11</v>
       </c>
       <c r="AE6" t="n">
-        <v>5.785082990428236e-08</v>
+        <v>9.680412027535112e-10</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.846342349651422e-08</v>
+        <v>1.199966015441589e-09</v>
       </c>
       <c r="AG6" t="n">
-        <v>8.860241962338478e-08</v>
+        <v>8.252887262472086e-10</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.276148501958232e-08</v>
+        <v>8.990808098019443e-12</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.066249097902983e-07</v>
+        <v>5.41798828024298e-10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4.974732092932754e-08</v>
+        <v>1.753824863115483e-10</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.467179456289159e-07</v>
+        <v>9.366103725927388e-11</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.360296266739169e-07</v>
+        <v>5.378476553019595e-10</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.097726578171205e-08</v>
+        <v>3.68408248352381e-10</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.307288443110679e-09</v>
+        <v>4.179953605465414e-10</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.663198100412046e-08</v>
+        <v>1.735991905782441e-10</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.287024673501946e-07</v>
+        <v>3.64760971427458e-10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.095669404094224e-07</v>
+        <v>5.151133408709541e-10</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.438557575283994e-07</v>
+        <v>3.868481368574095e-10</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.624928434144749e-08</v>
+        <v>2.334977489137913e-10</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.075532172327257e-08</v>
+        <v>2.637872420496734e-10</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.343997382718953e-06</v>
+        <v>3.226697797842348e-09</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.99255971722323e-08</v>
+        <v>2.174727065096249e-10</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.097034664278908e-07</v>
+        <v>3.7946415454293e-10</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.685252328798015e-07</v>
+        <v>1.293538498536861e-09</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.495498266507639e-08</v>
+        <v>2.520489650326141e-10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.972487666535017e-07</v>
+        <v>6.960639009623293e-11</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.957897534855874e-08</v>
+        <v>6.751554315620467e-10</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.636455948528237e-08</v>
+        <v>2.248821545647317e-10</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.934906883136136e-08</v>
+        <v>1.057106208124381e-10</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.43281134418794e-07</v>
+        <v>2.398817776361195e-11</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.456001931885112e-07</v>
+        <v>6.856726297854721e-10</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.88651071653112e-07</v>
+        <v>5.233143918204064e-10</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.878450461845205e-07</v>
+        <v>3.099118739413598e-10</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.776483540856134e-07</v>
+        <v>1.525696236015506e-12</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.821715898131515e-07</v>
+        <v>4.684286847300712e-10</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2.336766726784845e-07</v>
+        <v>7.48816120221818e-10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.663174107439772e-08</v>
+        <v>3.401215142861957e-10</v>
       </c>
       <c r="BL6" t="n">
-        <v>3.468613556378841e-07</v>
+        <v>2.863070891478969e-10</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.138419799597614e-07</v>
+        <v>7.812289148922957e-10</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.016182290593861e-07</v>
+        <v>1.63807981068409e-10</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.96936367003309e-09</v>
+        <v>1.229171764371983e-10</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.23010709735172e-07</v>
+        <v>1.466033072716755e-09</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.286358894958539e-07</v>
+        <v>3.863856457009263e-10</v>
       </c>
       <c r="BR6" t="n">
-        <v>2.057674493016748e-07</v>
+        <v>2.648067320976111e-10</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.394223136941264e-08</v>
+        <v>3.273534221470698e-10</v>
       </c>
       <c r="BT6" t="n">
-        <v>3.392333169927042e-08</v>
+        <v>2.026648293629307e-10</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.744553360249483e-08</v>
+        <v>3.478306254134367e-10</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.85454324411694e-07</v>
+        <v>2.089019623952026e-09</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.397399529423637e-07</v>
+        <v>5.309452183466234e-11</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.297206750905389e-07</v>
+        <v>1.74620470860809e-10</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.23266460150262e-07</v>
+        <v>1.992069564860088e-10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.190131394603668e-07</v>
+        <v>2.607310478630609e-10</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.133038965572268e-08</v>
+        <v>1.053632958658568e-09</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.253630870223787e-07</v>
+        <v>3.655117597478608e-10</v>
       </c>
       <c r="CC6" t="n">
-        <v>8.056645128817763e-08</v>
+        <v>4.985868384821401e-10</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.523210606066641e-08</v>
+        <v>3.143713622755229e-10</v>
       </c>
       <c r="CE6" t="n">
-        <v>3.488260631456797e-07</v>
+        <v>1.178326103357108e-09</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.245680749661915e-07</v>
+        <v>1.455728315669091e-10</v>
       </c>
       <c r="CG6" t="n">
-        <v>8.183238264791726e-08</v>
+        <v>1.256802717453098e-10</v>
       </c>
       <c r="CH6" t="n">
-        <v>9.853289384409436e-08</v>
+        <v>6.528081963885768e-10</v>
       </c>
       <c r="CI6" t="n">
-        <v>6.093241466942345e-08</v>
+        <v>1.073938576956479e-10</v>
       </c>
       <c r="CJ6" t="n">
-        <v>5.009257719734705e-08</v>
+        <v>2.811165467075938e-10</v>
       </c>
       <c r="CK6" t="n">
-        <v>4.322449598248568e-08</v>
+        <v>3.975430262759261e-10</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.539811561064198e-08</v>
+        <v>2.244667646200682e-10</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.895702664318378e-07</v>
+        <v>1.099208279953245e-09</v>
       </c>
       <c r="CN6" t="n">
-        <v>3.85799125979247e-07</v>
+        <v>2.453968805937734e-09</v>
       </c>
       <c r="CO6" t="n">
-        <v>3.988582353287029e-09</v>
+        <v>5.553792425949666e-10</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.291413210286919e-07</v>
+        <v>4.851634372027291e-11</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.344106289659976e-07</v>
+        <v>3.569786133361674e-10</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.913251708174357e-07</v>
+        <v>5.385104584476608e-10</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.133457772084512e-07</v>
+        <v>6.672651875483382e-10</v>
       </c>
       <c r="CT6" t="n">
-        <v>4.162189384260273e-07</v>
+        <v>1.169767060993365e-11</v>
       </c>
       <c r="CU6" t="n">
-        <v>9.443976978218416e-08</v>
+        <v>3.478951293711674e-10</v>
       </c>
       <c r="CV6" t="n">
-        <v>3.250218583161768e-08</v>
+        <v>2.007489036115473e-10</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.929139100160683e-07</v>
+        <v>1.125502802068468e-09</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.460499703398455e-07</v>
+        <v>2.064955428870974e-10</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.509960441126168e-07</v>
+        <v>2.923189468262422e-10</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.162916518637758e-07</v>
+        <v>5.913419753866833e-10</v>
       </c>
       <c r="DA6" t="n">
-        <v>5.013554726929215e-08</v>
+        <v>9.611244439211575e-11</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.506234864085854e-08</v>
+        <v>3.34881261609965e-10</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.288545886131033e-08</v>
+        <v>3.798056591453047e-10</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.379874241067228e-09</v>
+        <v>3.719518026912283e-10</v>
       </c>
       <c r="DE6" t="n">
-        <v>9.263456490771205e-08</v>
+        <v>7.317251804472846e-10</v>
       </c>
       <c r="DF6" t="n">
-        <v>3.778061739012628e-07</v>
+        <v>1.850215258780707e-10</v>
       </c>
       <c r="DG6" t="n">
-        <v>5.250245749266469e-08</v>
+        <v>4.605265127577418e-11</v>
       </c>
       <c r="DH6" t="n">
-        <v>7.570123443656485e-07</v>
+        <v>5.121454926815261e-10</v>
       </c>
       <c r="DI6" t="n">
-        <v>2.585739480309712e-07</v>
+        <v>3.813159510368536e-11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.507618776486197e-07</v>
+        <v>4.773189621332108e-10</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.197184644752269e-07</v>
+        <v>5.260791802186304e-10</v>
       </c>
       <c r="DL6" t="n">
-        <v>8.111241811548098e-08</v>
+        <v>7.889700559537971e-10</v>
       </c>
       <c r="DM6" t="n">
-        <v>1.163423988259638e-07</v>
+        <v>8.729444944677311e-11</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.079583711316445e-07</v>
+        <v>5.895581245418668e-11</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.069023423700855e-07</v>
+        <v>5.981861117554388e-10</v>
       </c>
       <c r="DP6" t="n">
-        <v>2.307945976554038e-07</v>
+        <v>2.033445078986063e-10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.997825904709316e-09</v>
+        <v>1.690818873800737e-10</v>
       </c>
       <c r="DR6" t="n">
-        <v>1.637003776977508e-07</v>
+        <v>2.853758895859926e-10</v>
       </c>
       <c r="DS6" t="n">
-        <v>2.14781366025818e-07</v>
+        <v>6.476719160986022e-10</v>
       </c>
       <c r="DT6" t="n">
-        <v>1.211120803645827e-07</v>
+        <v>5.656669022080507e-10</v>
       </c>
       <c r="DU6" t="n">
-        <v>3.824892402803926e-08</v>
+        <v>2.164266543758231e-10</v>
       </c>
       <c r="DV6" t="n">
-        <v>1.643311620114218e-08</v>
+        <v>2.099930229704228e-10</v>
       </c>
       <c r="DW6" t="n">
-        <v>1.557701523324795e-09</v>
+        <v>9.030511061158819e-11</v>
       </c>
       <c r="DX6" t="n">
-        <v>5.173027872729108e-08</v>
+        <v>1.270853644541603e-09</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.95390411920016e-08</v>
+        <v>6.918274980671768e-11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.472342330861466e-09</v>
+        <v>1.957409373476438e-10</v>
       </c>
       <c r="EA6" t="n">
-        <v>2.480929879311589e-07</v>
+        <v>1.925123838120157e-09</v>
       </c>
       <c r="EB6" t="n">
-        <v>2.197858250951867e-08</v>
+        <v>8.064660050877137e-11</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.671388526527153e-08</v>
+        <v>9.5636776276109e-11</v>
       </c>
       <c r="ED6" t="n">
-        <v>4.016056465161455e-08</v>
+        <v>9.184226157366027e-10</v>
       </c>
       <c r="EE6" t="n">
-        <v>4.900132211105301e-08</v>
+        <v>8.677902840759089e-10</v>
       </c>
       <c r="EF6" t="n">
-        <v>5.824291093858847e-08</v>
+        <v>4.349084425925298e-10</v>
       </c>
       <c r="EG6" t="n">
-        <v>2.188971848227084e-07</v>
+        <v>3.172562768050113e-10</v>
       </c>
       <c r="EH6" t="n">
-        <v>1.711346797605984e-08</v>
+        <v>9.170883497056082e-11</v>
       </c>
       <c r="EI6" t="n">
-        <v>1.591168938830378e-07</v>
+        <v>1.89880111634011e-10</v>
       </c>
       <c r="EJ6" t="n">
-        <v>4.079986481997366e-08</v>
+        <v>3.818401428379303e-10</v>
       </c>
       <c r="EK6" t="n">
-        <v>3.218895727741256e-08</v>
+        <v>1.994072684752268e-10</v>
       </c>
       <c r="EL6" t="n">
-        <v>6.050338186014415e-08</v>
+        <v>5.571652028635299e-10</v>
       </c>
       <c r="EM6" t="n">
-        <v>2.428967960099726e-08</v>
+        <v>3.194312869769789e-10</v>
       </c>
       <c r="EN6" t="n">
-        <v>2.643924190692815e-09</v>
+        <v>4.485515292529385e-10</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.129449600512089e-07</v>
+        <v>4.327872088483176e-11</v>
       </c>
       <c r="EP6" t="n">
-        <v>1.796784658836259e-07</v>
+        <v>5.360495936024279e-10</v>
       </c>
       <c r="EQ6" t="n">
-        <v>1.49514463032574e-07</v>
+        <v>2.872279497578845e-11</v>
       </c>
       <c r="ER6" t="n">
-        <v>7.556725734048086e-08</v>
+        <v>1.741650157427443e-10</v>
       </c>
       <c r="ES6" t="n">
-        <v>8.739973367255516e-08</v>
+        <v>4.381301987876896e-10</v>
       </c>
       <c r="ET6" t="n">
-        <v>3.113987361302861e-07</v>
+        <v>2.869168791441723e-11</v>
       </c>
       <c r="EU6" t="n">
-        <v>2.079726257875336e-08</v>
+        <v>3.062207432069641e-11</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.495782129268264e-07</v>
+        <v>3.672664949938564e-10</v>
       </c>
       <c r="EW6" t="n">
-        <v>1.450985109840985e-08</v>
+        <v>4.280676091372726e-10</v>
       </c>
       <c r="EX6" t="n">
-        <v>1.242964664527335e-08</v>
+        <v>2.951949795715336e-10</v>
       </c>
       <c r="EY6" t="n">
-        <v>2.941267496225919e-07</v>
+        <v>1.197844712308438e-09</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1.011251029581217e-07</v>
+        <v>1.290237083839685e-10</v>
       </c>
       <c r="FA6" t="n">
-        <v>1.023378857212265e-07</v>
+        <v>1.709220681656021e-10</v>
       </c>
       <c r="FB6" t="n">
-        <v>3.993591235484928e-08</v>
+        <v>4.249505192177594e-10</v>
       </c>
       <c r="FC6" t="n">
-        <v>9.579905224654794e-08</v>
+        <v>1.298409713079707e-10</v>
       </c>
       <c r="FD6" t="n">
-        <v>5.011944637089982e-08</v>
+        <v>1.036546820598616e-10</v>
       </c>
       <c r="FE6" t="n">
-        <v>2.167743495817831e-08</v>
+        <v>3.762247735572544e-10</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.057522152654201e-08</v>
+        <v>4.262206976246574e-10</v>
       </c>
       <c r="FG6" t="n">
-        <v>6.037480915210836e-08</v>
+        <v>2.66603183973757e-10</v>
       </c>
       <c r="FH6" t="n">
-        <v>1.013855452924872e-07</v>
+        <v>2.849919744640772e-10</v>
       </c>
       <c r="FI6" t="n">
-        <v>3.05370662090354e-08</v>
+        <v>4.704534539712313e-10</v>
       </c>
       <c r="FJ6" t="n">
-        <v>1.914944505188032e-07</v>
+        <v>7.043158278818851e-10</v>
       </c>
       <c r="FK6" t="n">
-        <v>6.731120549829939e-08</v>
+        <v>3.638266354855091e-10</v>
       </c>
       <c r="FL6" t="n">
-        <v>1.032567382708294e-07</v>
+        <v>5.465324304232411e-10</v>
       </c>
       <c r="FM6" t="n">
-        <v>2.117868405093759e-07</v>
+        <v>3.075135701635645e-10</v>
       </c>
       <c r="FN6" t="n">
-        <v>2.976429591683427e-08</v>
+        <v>1.125501136733931e-09</v>
       </c>
       <c r="FO6" t="n">
-        <v>2.045468505684767e-08</v>
+        <v>4.53716841875007e-10</v>
       </c>
       <c r="FP6" t="n">
-        <v>1.158459070893514e-07</v>
+        <v>6.320794998515566e-10</v>
       </c>
       <c r="FQ6" t="n">
-        <v>9.823245505913292e-08</v>
+        <v>8.684641894518563e-10</v>
       </c>
       <c r="FR6" t="n">
-        <v>6.281229758542395e-08</v>
+        <v>2.794554865293009e-10</v>
       </c>
       <c r="FS6" t="n">
-        <v>1.905019075820746e-07</v>
+        <v>9.283118718173e-10</v>
       </c>
       <c r="FT6" t="n">
-        <v>2.695864154134142e-08</v>
+        <v>1.654511666560055e-10</v>
       </c>
       <c r="FU6" t="n">
-        <v>5.074917908132193e-08</v>
+        <v>5.094152322193679e-10</v>
       </c>
       <c r="FV6" t="n">
-        <v>4.59751277048781e-08</v>
+        <v>5.62818180949165e-10</v>
       </c>
       <c r="FW6" t="n">
-        <v>5.040763539909676e-08</v>
+        <v>1.604057719983842e-10</v>
       </c>
       <c r="FX6" t="n">
-        <v>7.865138229590229e-08</v>
+        <v>3.424160954779154e-10</v>
       </c>
       <c r="FY6" t="n">
-        <v>1.188688898423607e-07</v>
+        <v>2.81872719609666e-11</v>
       </c>
       <c r="FZ6" t="n">
-        <v>1.136811675905847e-07</v>
+        <v>6.655481721296042e-10</v>
       </c>
       <c r="GA6" t="n">
-        <v>1.7017343623138e-07</v>
+        <v>2.690401512683849e-10</v>
       </c>
       <c r="GB6" t="n">
-        <v>4.207347714668686e-08</v>
+        <v>4.75411585099117e-11</v>
       </c>
       <c r="GC6" t="n">
-        <v>1.148156201224992e-07</v>
+        <v>1.03523389860527e-09</v>
       </c>
       <c r="GD6" t="n">
-        <v>2.640979346324457e-07</v>
+        <v>4.545576692827069e-10</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.28638043608953e-07</v>
+        <v>1.316229902847965e-09</v>
       </c>
       <c r="GF6" t="n">
-        <v>4.942754827652607e-08</v>
+        <v>3.359107714206999e-10</v>
       </c>
       <c r="GG6" t="n">
-        <v>5.33923305567896e-08</v>
+        <v>4.510340434471516e-10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001274619135074317</v>
+        <v>9.253667667508125e-05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.008648223243653774</v>
+        <v>0.0004533524916041642</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003574918955564499</v>
+        <v>9.523384505882859e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004000662826001644</v>
+        <v>9.396364475833252e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.402980342390947e-05</v>
+        <v>0.000158870592713356</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003833565395325422</v>
+        <v>0.0001298663846682757</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003521395847201347</v>
+        <v>7.966519660840277e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009861703729256988</v>
+        <v>6.425002356991172e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002552771475166082</v>
+        <v>6.346270674839616e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002371095353737473</v>
+        <v>7.088625716278329e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00587619049474597</v>
+        <v>0.000666674692183733</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003671037266030908</v>
+        <v>0.000117060226330068</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004107219167053699</v>
+        <v>7.650107727386057e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0008269344107247889</v>
+        <v>0.0001704534515738487</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004759902600198984</v>
+        <v>4.37331764260307e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002724344667512923</v>
+        <v>3.948530502384529e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.768863436765969e-05</v>
+        <v>6.273782491916791e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002286279632244259</v>
+        <v>8.274440187960863e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004243828007020056</v>
+        <v>2.397184653091244e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0007964905817061663</v>
+        <v>4.757827991852537e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0004678988188970834</v>
+        <v>1.700194479781203e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001294960267841816</v>
+        <v>5.641755706164986e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0006126515800133348</v>
+        <v>4.524096948443912e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>8.688405068824068e-05</v>
+        <v>2.476327608746942e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0006466277991421521</v>
+        <v>1.930396501848008e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000340486818458885</v>
+        <v>6.291411409620196e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0006350333569571376</v>
+        <v>8.169405919034034e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004111782182008028</v>
+        <v>3.195129829691723e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001500144484452903</v>
+        <v>5.196928395889699e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.953647294314578e-05</v>
+        <v>5.113499719300307e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>8.754195732763037e-05</v>
+        <v>1.541655728942715e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0005981723661534488</v>
+        <v>0.0001253083464689553</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.784110493957996e-05</v>
+        <v>3.079420639551245e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0006025226321071386</v>
+        <v>1.267229981749551e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003595562884584069</v>
+        <v>9.209301060764119e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0003030186053365469</v>
+        <v>4.098543286090717e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0008497777744196355</v>
+        <v>3.64342031389242e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0009146069642156363</v>
+        <v>8.784927922533825e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>7.844164792913944e-05</v>
+        <v>3.219749123672955e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0006440500728785992</v>
+        <v>3.096359068877064e-05</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0005459262174554169</v>
+        <v>3.599970295908861e-05</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001341351307928562</v>
+        <v>2.339869206480216e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0001132009638240561</v>
+        <v>2.991306610056199e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.000193337255041115</v>
+        <v>4.800646274816245e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0005297574098221958</v>
+        <v>8.478108611598145e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0001969610748346895</v>
+        <v>5.603583849733695e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.005862730089575052</v>
+        <v>0.0004566300194710493</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0005048141465522349</v>
+        <v>3.941305476473644e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0006664652028121054</v>
+        <v>6.700111043755896e-06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0007325788610614836</v>
+        <v>0.000103440645034425</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001741199870593846</v>
+        <v>5.329604391590692e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.168835635529831e-05</v>
+        <v>1.996737864828901e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0001395284925820306</v>
+        <v>2.043391941697337e-05</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001003254787065089</v>
+        <v>3.628748891060241e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0002113991067744792</v>
+        <v>5.480500112753361e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.001624403987079859</v>
+        <v>7.347021892201155e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.00182829424738884</v>
+        <v>7.583961996715516e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001620904076844454</v>
+        <v>2.478894566593226e-05</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001264213817194104</v>
+        <v>9.26665888982825e-05</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.001236097887158394</v>
+        <v>5.13822706125211e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0005286131636239588</v>
+        <v>3.505916174617596e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001037435606122017</v>
+        <v>5.335988680599257e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0002344836248084903</v>
+        <v>1.339552181889303e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0007215074147097766</v>
+        <v>3.03042743325932e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.001261322293430567</v>
+        <v>5.316000169841573e-06</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0005117658874951303</v>
+        <v>1.072213672159705e-05</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0009536703582853079</v>
+        <v>4.572366015054286e-05</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0009692044113762677</v>
+        <v>7.666669262107462e-05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0002154465764760971</v>
+        <v>7.091567567840684e-06</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0004554920888040215</v>
+        <v>8.319332846440375e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0006054490804672241</v>
+        <v>3.293261761427857e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003359392576385289</v>
+        <v>8.332504876307212e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0002905433939304203</v>
+        <v>3.002903031301685e-05</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.002761810552328825</v>
+        <v>0.0002796584158204496</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.00038606469752267</v>
+        <v>5.154296559339855e-06</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0006183668738231063</v>
+        <v>6.816401582909748e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004009872791357338</v>
+        <v>3.165117595926858e-05</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0003637380432337523</v>
+        <v>5.179595973459072e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0002918447135016322</v>
+        <v>4.125590930925682e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.475499059073627e-05</v>
+        <v>5.165804395801388e-06</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0006302893743850291</v>
+        <v>6.774161010980606e-05</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0004928690032102168</v>
+        <v>1.290943055209937e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001522589707747102</v>
+        <v>0.0001658451510593295</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0006662448868155479</v>
+        <v>2.666740692802705e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.000360464007826522</v>
+        <v>7.561905022157589e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.000426554266596213</v>
+        <v>1.394956143485615e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0006360559491440654</v>
+        <v>5.622598837362602e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0002630181552376598</v>
+        <v>1.358593453915091e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0003283199912402779</v>
+        <v>1.884522134787403e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0003664926334749907</v>
+        <v>1.325342600466684e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0008203026372939348</v>
+        <v>3.546445077518001e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0001972869940800592</v>
+        <v>0.0002504947478882968</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0006731631001457572</v>
+        <v>2.219393172708806e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0006348605384118855</v>
+        <v>5.372521263780072e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0004035474266856909</v>
+        <v>2.690288965823129e-05</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.001196202007122338</v>
+        <v>8.773840818321332e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0007029476691968739</v>
+        <v>1.422617697244277e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0007899240590631962</v>
+        <v>7.774840923957527e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0003663156530819833</v>
+        <v>2.674952702363953e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0003977347805630416</v>
+        <v>6.145328370621428e-07</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.001151865464635193</v>
+        <v>0.0001593114866409451</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0007158964872360229</v>
+        <v>1.909561615320854e-05</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0007955031469464302</v>
+        <v>9.105020581046119e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0003825993626378477</v>
+        <v>1.055269967764616e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0006264019757509232</v>
+        <v>5.601663724519312e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0003056378627661616</v>
+        <v>4.87263150716899e-06</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0005783392698504031</v>
+        <v>2.305870475538541e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001711437071207911</v>
+        <v>3.897750866599381e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0007822696352377534</v>
+        <v>6.484040932264179e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0009705488919280469</v>
+        <v>2.453922570566647e-05</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0002528569602873176</v>
+        <v>9.048225365404505e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001944590942002833</v>
+        <v>2.120580393238924e-05</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0007297383854165673</v>
+        <v>1.617011912458111e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>8.035288192331791e-05</v>
+        <v>0.0001820556062739342</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0007687965407967567</v>
+        <v>3.216758341295645e-05</v>
       </c>
       <c r="DL7" t="n">
-        <v>2.797594061121345e-05</v>
+        <v>3.757578815566376e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.000266840128460899</v>
+        <v>2.985548780998215e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0007120574591681361</v>
+        <v>1.001302734948695e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0004990482120774686</v>
+        <v>7.316820119740441e-05</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.001037551905028522</v>
+        <v>2.082113132928498e-05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0005778908962383866</v>
+        <v>6.493904948001727e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.549691458232701e-05</v>
+        <v>9.213564226229209e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0009292842587456107</v>
+        <v>5.780925675935578e-06</v>
       </c>
       <c r="DT7" t="n">
-        <v>6.16451507085003e-05</v>
+        <v>8.782868690104806e-07</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0001485116663388908</v>
+        <v>7.790665404172614e-05</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.000577739265281707</v>
+        <v>9.634194429963827e-05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0003693390754051507</v>
+        <v>3.450213625910692e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0002059006073977798</v>
+        <v>0.000137853974592872</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.001409413758665323</v>
+        <v>7.339809599216096e-06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0001140050080721267</v>
+        <v>3.891259257216007e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0004595008213073015</v>
+        <v>3.050623126910068e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0002980166464112699</v>
+        <v>0.0001537223579362035</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001010359410429373</v>
+        <v>6.825766377005493e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>1.553264155518264e-05</v>
+        <v>6.630960706388578e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>7.521120278397575e-05</v>
+        <v>6.479769945144653e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>4.793264088220894e-05</v>
+        <v>3.107691736659035e-05</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.000744546705391258</v>
+        <v>8.28189222374931e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001276418915949762</v>
+        <v>2.692263842618559e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.000352362374542281</v>
+        <v>1.977620922843926e-05</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001748225331539288</v>
+        <v>5.791931471321732e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.00047943732351996</v>
+        <v>3.164766530971974e-05</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0002420287346467376</v>
+        <v>7.206579994090134e-06</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0001346099306829274</v>
+        <v>3.301708056824282e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001832874113461003</v>
+        <v>1.866182356025092e-05</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0005347867263481021</v>
+        <v>1.990993405343033e-05</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.000905183725990355</v>
+        <v>6.718079384882003e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0001318165741395205</v>
+        <v>1.279845309909433e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0008186554186977446</v>
+        <v>7.666229066671804e-06</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0004666580935008824</v>
+        <v>4.81112401757855e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.001948699005879462</v>
+        <v>3.792101051658392e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0005787221016362309</v>
+        <v>2.000468339247163e-05</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.001478765509091318</v>
+        <v>9.81718949333299e-06</v>
       </c>
       <c r="EW7" t="n">
-        <v>2.057491656159982e-05</v>
+        <v>2.784208845696412e-07</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0003685686970129609</v>
+        <v>2.259421307826415e-06</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.001123024150729179</v>
+        <v>0.0001864070945885032</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0003995911392848939</v>
+        <v>2.628972470120061e-05</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0004739156574942172</v>
+        <v>1.134065860242117e-05</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0003599037590902299</v>
+        <v>1.032492491503945e-06</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0006508997175842524</v>
+        <v>6.052663593436591e-05</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0004170291940681636</v>
+        <v>1.207867717312183e-05</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0003821807913482189</v>
+        <v>1.567634899402037e-05</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0003895609988830984</v>
+        <v>3.401848880457692e-05</v>
       </c>
       <c r="FG7" t="n">
-        <v>7.44037824915722e-05</v>
+        <v>4.00342614739202e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0006623876397497952</v>
+        <v>4.714532042271458e-05</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.0006374089862219989</v>
+        <v>5.949976548436098e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0006369061302393675</v>
+        <v>6.822311843279749e-05</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0001893826702143997</v>
+        <v>4.743555564346025e-06</v>
       </c>
       <c r="FL7" t="n">
-        <v>1.685023016761988e-05</v>
+        <v>3.916794230462983e-05</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0002299842017237097</v>
+        <v>4.122041718801484e-05</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.0003059088485315442</v>
+        <v>3.001430013682693e-05</v>
       </c>
       <c r="FO7" t="n">
-        <v>7.303458551177755e-05</v>
+        <v>8.344109664903954e-05</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0009452967788092792</v>
+        <v>3.96257164538838e-05</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0006527621299028397</v>
+        <v>3.303805715404451e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0002185313787776977</v>
+        <v>9.96828566712793e-06</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0002458540257066488</v>
+        <v>8.754192822379991e-05</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001823091297410429</v>
+        <v>3.291289249318652e-05</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0006669425638392568</v>
+        <v>1.65094570547808e-05</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0002636504650581628</v>
+        <v>6.509662853204645e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0001265401660930365</v>
+        <v>4.91899554617703e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.423143450869247e-05</v>
+        <v>8.939787221606821e-05</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.00093322794418782</v>
+        <v>1.508654895587824e-05</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0005777275655418634</v>
+        <v>6.581579509656876e-05</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0006469868822023273</v>
+        <v>2.812805905705318e-05</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0003830748610198498</v>
+        <v>6.524498166982085e-05</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0006380807608366013</v>
+        <v>4.841920963372104e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0007918037008494139</v>
+        <v>2.029843926720787e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.00228847423568368</v>
+        <v>8.648778020869941e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>6.844368181191385e-05</v>
+        <v>9.182247595163062e-05</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0003762194828595966</v>
+        <v>7.675300730625167e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.02357611060142517</v>
+        <v>0.00747733935713768</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01263582054525614</v>
+        <v>0.003031927393749356</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03075169585645199</v>
+        <v>0.01726643741130829</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02462064474821091</v>
+        <v>0.03163701668381691</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001194362062960863</v>
+        <v>0.02191551402211189</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004450631327927113</v>
+        <v>0.003482611384242773</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003218917176127434</v>
+        <v>0.001773378811776638</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01786834932863712</v>
+        <v>0.01097459811717272</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00124801998026669</v>
+        <v>1.023570075631142e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02872246876358986</v>
+        <v>0.005815411917865276</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0192504245787859</v>
+        <v>0.002494571730494499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02425015158951283</v>
+        <v>0.01531279552727938</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02075961045920849</v>
+        <v>0.03019054606556892</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01399863138794899</v>
+        <v>0.02140370011329651</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001017820555716753</v>
+        <v>0.007312422152608633</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004845461342483759</v>
+        <v>0.01308183837682009</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01768901199102402</v>
+        <v>0.02632946893572807</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005269333720207214</v>
+        <v>0.002132953144609928</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009055765345692635</v>
+        <v>0.0009772313060238957</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0007032022695057094</v>
+        <v>0.007039656396955252</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0001747102069202811</v>
+        <v>0.002429127460345626</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003284639096818864</v>
+        <v>0.006630230695009232</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01453875284641981</v>
+        <v>0.002739458810538054</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002473364118486643</v>
+        <v>0.01862325519323349</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00113179290201515</v>
+        <v>0.004536539316177368</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01569246873259544</v>
+        <v>0.001996043371036649</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003596426686272025</v>
+        <v>0.003524947445839643</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004980270168744028</v>
+        <v>0.002417938550934196</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01170468609780073</v>
+        <v>0.0009154530707746744</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0004431753768585622</v>
+        <v>0.007331306114792824</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002418249845504761</v>
+        <v>0.0004348433576524258</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003066736273467541</v>
+        <v>0.01714820228517056</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001813160022720695</v>
+        <v>0.0006320074899122119</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002984070917591453</v>
+        <v>0.0001172833144664764</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.004350835457444191</v>
+        <v>0.01349809858947992</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004572055302560329</v>
+        <v>0.005152171477675438</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001483764965087175</v>
+        <v>0.008222763426601887</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.003475263947620988</v>
+        <v>0.005696266423910856</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.001481628627516329</v>
+        <v>0.008359710685908794</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.003457851707935333</v>
+        <v>0.01317342184484005</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.00121423345990479</v>
+        <v>0.006367768160998821</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.003584857098758221</v>
+        <v>0.002378581557422876</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.005556276068091393</v>
+        <v>0.0006405608728528023</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0004501293879002333</v>
+        <v>0.0040436708368361</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0007837535813450813</v>
+        <v>0.002140584867447615</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002469613216817379</v>
+        <v>0.01590860262513161</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.005726655479520559</v>
+        <v>0.001181573141366243</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.01845933124423027</v>
+        <v>0.03146305680274963</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0228929165750742</v>
+        <v>0.03536810725927353</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.004403391852974892</v>
+        <v>0.02474047802388668</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.006282790564000607</v>
+        <v>0.01418772712349892</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.004203883931040764</v>
+        <v>0.01228244043886662</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.01041143201291561</v>
+        <v>0.008550867438316345</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004765556659549475</v>
+        <v>0.007781655061990023</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.02617190405726433</v>
+        <v>0.01549478340893984</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01221660152077675</v>
+        <v>0.003485900815576315</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.003645496210083365</v>
+        <v>0.008832567371428013</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003974491264671087</v>
+        <v>0.02195238135755062</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01724426448345184</v>
+        <v>0.0160730816423893</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0005503108259290457</v>
+        <v>0.01398790255188942</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01291119400411844</v>
+        <v>0.003879423718899488</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.02863318845629692</v>
+        <v>0.003068186342716217</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0006710337474942207</v>
+        <v>0.01120346318930387</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0009707508143037558</v>
+        <v>0.002811799291521311</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.006624556146562099</v>
+        <v>0.007388909347355366</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.006043773144483566</v>
+        <v>0.000242191250436008</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.008651827462017536</v>
+        <v>0.01082069054245949</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01552856341004372</v>
+        <v>0.01107243914157152</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.002995621878653765</v>
+        <v>0.003663427662104368</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.00621365662664175</v>
+        <v>0.005479402840137482</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.003186721820384264</v>
+        <v>0.004756955429911613</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.006498541217297316</v>
+        <v>0.005290722008794546</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002794137690216303</v>
+        <v>0.003118829103186727</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.007635128684341908</v>
+        <v>0.00481354258954525</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.009022611193358898</v>
+        <v>0.01347864791750908</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.006082565058022738</v>
+        <v>0.01980271935462952</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.007679054513573647</v>
+        <v>0.01045581232756376</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.000761712493840605</v>
+        <v>0.00431289616972208</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.004971026442945004</v>
+        <v>0.006628274917602539</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.01787272095680237</v>
+        <v>0.002211834769695997</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.005576075054705143</v>
+        <v>0.001836145296692848</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.005259108729660511</v>
+        <v>0.001038519199937582</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.003930516541004181</v>
+        <v>0.001191228628158569</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.006732193753123283</v>
+        <v>0.006053025368601084</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004600830841809511</v>
+        <v>0.007843859493732452</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.004424207378178835</v>
+        <v>0.004898109938949347</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.002434681402519345</v>
+        <v>0.003206470282748342</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003198973834514618</v>
+        <v>0.00223931111395359</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00443213852122426</v>
+        <v>0.001702232984825969</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.004186843056231737</v>
+        <v>0.001852541230618954</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.008316732943058014</v>
+        <v>0.005190062336623669</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.002080926205962896</v>
+        <v>0.003814951283857226</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001861040713265538</v>
+        <v>0.007250577211380005</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001496664830483496</v>
+        <v>0.003106134943664074</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.007295011542737484</v>
+        <v>0.02559478767216206</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002104598097503185</v>
+        <v>0.009973949752748013</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.002819756511598825</v>
+        <v>0.003701323876157403</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.005053635686635971</v>
+        <v>0.006211721338331699</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.007489915005862713</v>
+        <v>0.006706859916448593</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.00552251236513257</v>
+        <v>0.001887009129859507</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.001832949812524021</v>
+        <v>0.002264834940433502</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.00349504197947681</v>
+        <v>0.004568375647068024</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.002949540736153722</v>
+        <v>0.007322314195334911</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.004035592079162598</v>
+        <v>0.006434019654989243</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.001849104301072657</v>
+        <v>0.00603471789509058</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001121025532484055</v>
+        <v>0.001896348665468395</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.003480604384094477</v>
+        <v>0.00169488147366792</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.004583805333822966</v>
+        <v>0.0009588634711690247</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0007234690710902214</v>
+        <v>0.009998707100749016</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.01677554287016392</v>
+        <v>0.008340490981936455</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.006214278750121593</v>
+        <v>0.01503412704914808</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.00556491781026125</v>
+        <v>0.0007869978435337543</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.002707711420953274</v>
+        <v>0.006032766774296761</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.02048530243337154</v>
+        <v>0.01941149868071079</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.02060291916131973</v>
+        <v>0.006181748583912849</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.002396105555817485</v>
+        <v>0.01534449309110641</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.006861578673124313</v>
+        <v>0.0002216731663793325</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.005247130990028381</v>
+        <v>0.008964431472122669</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.003380457870662212</v>
+        <v>0.0003298262017779052</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.009455475024878979</v>
+        <v>0.0008010014425963163</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0006037660059519112</v>
+        <v>0.006778398528695107</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.009948629885911942</v>
+        <v>0.01078645326197147</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0005409631412476301</v>
+        <v>0.0008602715097367764</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.005709579680114985</v>
+        <v>0.0008380364160984755</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.004222911316901445</v>
+        <v>0.0002344376407563686</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0020344911608845</v>
+        <v>0.003200586652383208</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0006062830798327923</v>
+        <v>0.013975421898067</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.002182701602578163</v>
+        <v>0.0001680126879364252</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.00523867504671216</v>
+        <v>0.006202741991728544</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.001627186080440879</v>
+        <v>0.007739922031760216</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001571666914969683</v>
+        <v>0.006912966724485159</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.01255657523870468</v>
+        <v>0.008632450364530087</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.002084634499624372</v>
+        <v>0.004920640029013157</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.008139705285429955</v>
+        <v>0.01288897171616554</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.008770661428570747</v>
+        <v>0.009943746961653233</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.004774563945829868</v>
+        <v>0.0009303289116360247</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.002150565152987838</v>
+        <v>0.0006673347670584917</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.006362913176417351</v>
+        <v>0.0009011275251396</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.005922615993767977</v>
+        <v>0.00472453935071826</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.002329678740352392</v>
+        <v>0.006763009820133448</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.003799236146733165</v>
+        <v>0.002579642226919532</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.00267522013746202</v>
+        <v>0.002622916828840971</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.004959108307957649</v>
+        <v>0.002653721952810884</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.007808996364474297</v>
+        <v>0.002084621693938971</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.002473820466548204</v>
+        <v>0.002641899278387427</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.000558667816221714</v>
+        <v>0.002540936693549156</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.00680936872959137</v>
+        <v>0.0007709661149419844</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.00348296482115984</v>
+        <v>0.005310396663844585</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.002695228438824415</v>
+        <v>0.003882559947669506</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0004640219267457724</v>
+        <v>0.01291064545512199</v>
       </c>
       <c r="EU8" t="n">
-        <v>3.877094422932714e-05</v>
+        <v>0.003162093926221132</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.01448117289692163</v>
+        <v>0.003361980663612485</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.001357408124022186</v>
+        <v>0.00124009104911238</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.004192456603050232</v>
+        <v>0.001210265909321606</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.00282880337908864</v>
+        <v>0.002000030130147934</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.004975600633770227</v>
+        <v>0.005230233073234558</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.002835764549672604</v>
+        <v>0.008986357599496841</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002625557826831937</v>
+        <v>0.006058307364583015</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.002073190407827497</v>
+        <v>0.004529915750026703</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.001627662335522473</v>
+        <v>0.00270290463231504</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.003287554252892733</v>
+        <v>0.004621811676770449</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.005446123890578747</v>
+        <v>0.0004819947062060237</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.001829192158766091</v>
+        <v>0.002753358334302902</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0007833786075934768</v>
+        <v>0.003119524568319321</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.002035240875557065</v>
+        <v>0.007187368348240852</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.006482221186161041</v>
+        <v>0.008869601413607597</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.007636894937604666</v>
+        <v>0.003646427765488625</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.006509840488433838</v>
+        <v>0.006151658482849598</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.005636225920170546</v>
+        <v>0.004445688799023628</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.002994238631799817</v>
+        <v>0.008671142160892487</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.01069736573845148</v>
+        <v>0.002707646228373051</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01500693894922733</v>
+        <v>0.006674180738627911</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.00644821859896183</v>
+        <v>0.01343178283423185</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.01910307630896568</v>
+        <v>0.001108902739360929</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.005142886191606522</v>
+        <v>0.01365353725850582</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001947794575244188</v>
+        <v>0.009215189144015312</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.008119296282529831</v>
+        <v>0.003206119872629642</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.003948796540498734</v>
+        <v>0.01546953618526459</v>
       </c>
       <c r="FW8" t="n">
-        <v>8.177291601896286e-05</v>
+        <v>0.009905638173222542</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.00616740295663476</v>
+        <v>0.004342327825725079</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.00391846802085638</v>
+        <v>0.00422479584813118</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.001451608492061496</v>
+        <v>0.005588467698544264</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.004415411967784166</v>
+        <v>0.003522350452840328</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.006687107961624861</v>
+        <v>0.008149591274559498</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.004109063651412725</v>
+        <v>0.01094484515488148</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01077213976532221</v>
+        <v>0.008895223960280418</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.00126986566465348</v>
+        <v>0.009327482432126999</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.002815498504787683</v>
+        <v>0.001124338479712605</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0009939237497746944</v>
+        <v>0.001710384851321578</v>
       </c>
     </row>
     <row r="9">
@@ -5551,4554 +5551,4554 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.002413928741589189</v>
+        <v>0.001790279522538185</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0226025078445673</v>
+        <v>0.003688742872327566</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00231997505761683</v>
+        <v>0.000583929882850498</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01060517784208059</v>
+        <v>0.0004651581111829728</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005626839585602283</v>
+        <v>0.0008463736157864332</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01309729740023613</v>
+        <v>0.002539864042773843</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001327273203060031</v>
+        <v>0.0003528667148202658</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004926357883960009</v>
+        <v>0.0002672059345059097</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003904500044882298</v>
+        <v>0.0001207265595439821</v>
       </c>
       <c r="J10" t="n">
-        <v>0.003628264646977186</v>
+        <v>0.001407589297741652</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01792416162788868</v>
+        <v>0.004643495660275221</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008327607065439224</v>
+        <v>0.0008643011096864939</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01008464861661196</v>
+        <v>0.0004380634054541588</v>
       </c>
       <c r="N10" t="n">
-        <v>0.006645519752055407</v>
+        <v>0.000487887067720294</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01587011478841305</v>
+        <v>0.00268184719607234</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002663638675585389</v>
+        <v>0.0007244602311402559</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.003955737687647343</v>
+        <v>0.00127212586812675</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00148102396633476</v>
+        <v>0.0008654560660943389</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001565819606184959</v>
+        <v>0.0002852457691915333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.004404434934258461</v>
+        <v>0.0004397050361149013</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001772739458829165</v>
+        <v>0.0006057666032575071</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002149173291400075</v>
+        <v>0.0008231980027630925</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001560987904667854</v>
+        <v>0.0004300224536564201</v>
       </c>
       <c r="X10" t="n">
-        <v>0.002077231649309397</v>
+        <v>0.0001369314850308001</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001819615950807929</v>
+        <v>0.0001651814964134246</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0008544971933588386</v>
+        <v>0.0008364314562641084</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001962356269359589</v>
+        <v>3.959508831030689e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0007475269958376884</v>
+        <v>0.0003450211079325527</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.003272732021287084</v>
+        <v>0.0005115652456879616</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.001459278049878776</v>
+        <v>0.0001166937290690839</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.002227455377578735</v>
+        <v>0.0007789571536704898</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0008670970564708114</v>
+        <v>0.001345994765870273</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002313136821612716</v>
+        <v>0.0005991697544232011</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.003502755658701062</v>
+        <v>0.0004430835542734712</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.001023422461003065</v>
+        <v>0.001205305568873882</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001212039263918996</v>
+        <v>0.0003860403667204082</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.003073185216635466</v>
+        <v>0.0001160674437414855</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.004541690461337566</v>
+        <v>0.00052090227836743</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0008298699394799769</v>
+        <v>0.0007934963214211166</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0008152892114594579</v>
+        <v>0.0008070198819041252</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0005525397136807442</v>
+        <v>0.0002451623440720141</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.002751318039372563</v>
+        <v>0.0004905303940176964</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001792813534848392</v>
+        <v>0.000546191877219826</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001659546629525721</v>
+        <v>0.000642626138869673</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.002941366750746965</v>
+        <v>0.0001105126430047676</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.004011994693428278</v>
+        <v>0.0007406559307128191</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01817535050213337</v>
+        <v>0.003700037021189928</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.001039544004015625</v>
+        <v>0.0004784147022292018</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.001573645044118166</v>
+        <v>0.0004459850606508553</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0009859580313786864</v>
+        <v>0.0007807288784533739</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006572439335286617</v>
+        <v>0.001293519395403564</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001347528188489377</v>
+        <v>4.5290871639736e-06</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0061678197234869</v>
+        <v>0.0001406459632562473</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001737730577588081</v>
+        <v>0.0004128508444409817</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.001824995735660195</v>
+        <v>0.0001389228564221412</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.004169086925685406</v>
+        <v>6.932857650099322e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.005375776439905167</v>
+        <v>0.0005032316548749804</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001181549741886556</v>
+        <v>0.0004402265185490251</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.007705064956098795</v>
+        <v>9.597654570825398e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.004579867236316204</v>
+        <v>0.0006796523230150342</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.00094155891565606</v>
+        <v>0.0003987026284448802</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.007138527929782867</v>
+        <v>0.0006777086528018117</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0005648085498251021</v>
+        <v>0.0001187747693620622</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0003336041118018329</v>
+        <v>8.952346979640424e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.004812971688807011</v>
+        <v>0.001162173342891037</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.003187721595168114</v>
+        <v>0.0001890879357233644</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.004687507636845112</v>
+        <v>0.0002111105713993311</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.004061202518641949</v>
+        <v>0.001014535315334797</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001542260171845555</v>
+        <v>0.0007624379359185696</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.002421715762466192</v>
+        <v>0.001091608195565641</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001189652015455067</v>
+        <v>0.0001445040397811681</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002408637665212154</v>
+        <v>0.001050685648806393</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.002302473178133368</v>
+        <v>0.0001011346466839314</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.008788053877651691</v>
+        <v>0.002474180888384581</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.003831207286566496</v>
+        <v>0.0005204427288845181</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.001973119331523776</v>
+        <v>0.0008464382262900472</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0005065190489403903</v>
+        <v>0.0002732484717853367</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.001874902052804828</v>
+        <v>0.000891860225237906</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.002774922177195549</v>
+        <v>0.0006424328894354403</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003292976878583431</v>
+        <v>3.549642860889435e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.001887838821858168</v>
+        <v>2.151853550458327e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.336463123559952e-05</v>
+        <v>0.0007471034186892211</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.004137166775763035</v>
+        <v>0.001037012902088463</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002307208953425288</v>
+        <v>1.620796501811128e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002501618582755327</v>
+        <v>0.000176946326973848</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.001028600614517927</v>
+        <v>0.0005253960844129324</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.002297009108588099</v>
+        <v>0.000706821505445987</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001476762816309929</v>
+        <v>0.0002489767502993345</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0008331699064001441</v>
+        <v>0.0001747617934597656</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001154855010099709</v>
+        <v>0.000153678935021162</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.005680866073817015</v>
+        <v>5.146820330992341e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.003849310101941228</v>
+        <v>0.001937713357619941</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0004618924867827445</v>
+        <v>0.0005426018033176661</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.003700541099533439</v>
+        <v>0.0007176854414865375</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.003491905983537436</v>
+        <v>0.0005763510707765818</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0007586335996165872</v>
+        <v>0.0002871708711609244</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.00213381857611239</v>
+        <v>0.0004747926141135395</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.003235436975955963</v>
+        <v>0.000662201433442533</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0004803756892215461</v>
+        <v>0.0002322436193935573</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.00027556560235098</v>
+        <v>0.0005197337595745921</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.003356770612299442</v>
+        <v>0.0009345256257802248</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.002733909524977207</v>
+        <v>2.384081744821742e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.00374048319645226</v>
+        <v>0.000101777128293179</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0009641377255320549</v>
+        <v>0.0005510572227649391</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.002590385731309652</v>
+        <v>0.0006666498957201838</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001523800659924746</v>
+        <v>5.407624848885462e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.00230125430971384</v>
+        <v>0.0002645802160259336</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0005325675010681152</v>
+        <v>6.541177572216839e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.002251109341159463</v>
+        <v>0.0002718809992074966</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.006984805222600698</v>
+        <v>0.001098650274798274</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001350496313534677</v>
+        <v>0.0003222909872420132</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.006842407863587141</v>
+        <v>0.0006812653155066073</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0009235296747647226</v>
+        <v>0.001232222886756063</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0008446390856988728</v>
+        <v>0.0002258627500850707</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.007112070452421904</v>
+        <v>1.549648004584014e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.002213242929428816</v>
+        <v>0.0007053603185340762</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.002415730152279139</v>
+        <v>0.0008352797012776136</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.001497853198088706</v>
+        <v>0.0001588210288900882</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.003223027102649212</v>
+        <v>0.0006098395679146051</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0009009211789816618</v>
+        <v>0.0005436455830931664</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0020655517000705</v>
+        <v>0.0006752281915396452</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001850082306191325</v>
+        <v>0.0001726812915876508</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002227887744084001</v>
+        <v>0.000299355189781636</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0008304912480525672</v>
+        <v>2.024634159170091e-05</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0003520962200127542</v>
+        <v>0.0003866110055241734</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.001806814572773874</v>
+        <v>0.0004536136984825134</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0002799005014821887</v>
+        <v>0.0006406511529348791</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0001540413068141788</v>
+        <v>0.0001513462339062244</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.003521926235407591</v>
+        <v>4.406122025102377e-05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001328587881289423</v>
+        <v>5.15399660798721e-05</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.002030974254012108</v>
+        <v>0.0005295937298797071</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.002188648330047727</v>
+        <v>0.0003140923799946904</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.001259933691471815</v>
+        <v>0.0003027389757335186</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0006050647352822125</v>
+        <v>0.0004550477315206081</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.000191795639693737</v>
+        <v>0.001272223191335797</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.002735645975917578</v>
+        <v>0.0006902600871399045</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001568203791975975</v>
+        <v>0.0001990492746699601</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.001588047947734594</v>
+        <v>0.0001862244098447263</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.002029186114668846</v>
+        <v>4.198649548925459e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0003592072171159089</v>
+        <v>0.0007218265091069043</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001262644538655877</v>
+        <v>0.0002377355995122343</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.002406905870884657</v>
+        <v>7.570003799628466e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0003043353790417314</v>
+        <v>5.030607280787081e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0001271406363230199</v>
+        <v>8.373349555768073e-05</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.00146644888445735</v>
+        <v>0.0004069918359164149</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0001086877964553423</v>
+        <v>0.000383105652872473</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.003998904954642057</v>
+        <v>0.0001352760591544211</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.002373791532590985</v>
+        <v>0.000651483132969588</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.001535254996269941</v>
+        <v>0.001258738455362618</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.002723178826272488</v>
+        <v>0.0003792892093770206</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.002216367982327938</v>
+        <v>0.000117404997581616</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.004179897252470255</v>
+        <v>6.904797919560224e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0004071882576681674</v>
+        <v>0.000813035003375262</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0002292856224812567</v>
+        <v>0.0007532993331551552</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.002772770589217544</v>
+        <v>0.001175470999442041</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.002123138168826699</v>
+        <v>4.034991434309632e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.002680749865248799</v>
+        <v>8.142393198795617e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001312249922193587</v>
+        <v>0.0007180240354500711</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.002234139014035463</v>
+        <v>0.0005307095125317574</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.002175378147512674</v>
+        <v>0.0002246912772534415</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001238173805177212</v>
+        <v>0.0001879514893516898</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.001218474470078945</v>
+        <v>0.0002250860852655023</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.001666061230935156</v>
+        <v>0.0003681248635984957</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.003005728591233492</v>
+        <v>0.001082628150470555</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.003048863960430026</v>
+        <v>0.0002131703804479912</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001080542337149382</v>
+        <v>0.0009408805053681135</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.001010527485050261</v>
+        <v>0.0005082989810034633</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002826865296810865</v>
+        <v>0.001410369761288166</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0002000987879000604</v>
+        <v>0.0007277054246515036</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0001342270115856081</v>
+        <v>0.001050627790391445</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.001524746185168624</v>
+        <v>0.0005527760367840528</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.002144965576007962</v>
+        <v>9.578245226293802e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.003497663419693708</v>
+        <v>0.0009871363872662187</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.001113796373829246</v>
+        <v>0.0007208195747807622</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.004599488340318203</v>
+        <v>0.0004570236778818071</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.005301319994032383</v>
+        <v>0.0008709204266779125</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.002163793426007032</v>
+        <v>0.0001775709533831105</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001395117491483688</v>
+        <v>0.0006561102345585823</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.00253899535164237</v>
+        <v>0.0005603848258033395</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.000114559312351048</v>
+        <v>0.0004882424836978316</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0019506054231897</v>
+        <v>0.0008298263419419527</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.00238999561406672</v>
+        <v>0.0002576650877017528</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.001254789298400283</v>
+        <v>0.0004214482614770532</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.002636772580444813</v>
+        <v>0.000481309398310259</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.001314612105488777</v>
+        <v>0.0006444619502872229</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0031505455262959</v>
+        <v>0.0005356803303584456</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.008909157477319241</v>
+        <v>0.0002464414574205875</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.00481189601123333</v>
+        <v>0.0002965604653581977</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0008803685777820647</v>
+        <v>0.00083212333265692</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0007918140618130565</v>
+        <v>0.01540343090891838</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01422211062163115</v>
+        <v>0.1083763539791107</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002232483588159084</v>
+        <v>0.01428781170397997</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00731344148516655</v>
+        <v>0.06281396746635437</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004296678118407726</v>
+        <v>0.01571859605610371</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0030947495251894</v>
+        <v>0.01807905919849873</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001779771642759442</v>
+        <v>0.02912325412034988</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0008023690897971392</v>
+        <v>0.0186004750430584</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000567986280657351</v>
+        <v>0.005811212118715048</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001934042200446129</v>
+        <v>0.003157880622893572</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01122956164181232</v>
+        <v>0.1103342622518539</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004261017311364412</v>
+        <v>0.01919181644916534</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007039058022201061</v>
+        <v>0.08922114223241806</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004422882571816444</v>
+        <v>0.03934308886528015</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00362748745828867</v>
+        <v>0.007569349370896816</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0008046802249737084</v>
+        <v>0.02605769224464893</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001599003444425762</v>
+        <v>0.007651516236364841</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001474245102144778</v>
+        <v>0.009112229570746422</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003845908213406801</v>
+        <v>0.004448699299246073</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002543191658332944</v>
+        <v>0.01514347642660141</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0003068844671361148</v>
+        <v>0.004961179103702307</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0007814235868863761</v>
+        <v>0.007049775216728449</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0008238695445470512</v>
+        <v>0.01344100292772055</v>
       </c>
       <c r="X11" t="n">
-        <v>0.002660601167008281</v>
+        <v>0.01824411191046238</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.001561311073601246</v>
+        <v>0.005875892005860806</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0002568547497503459</v>
+        <v>0.01277663372457027</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.001215642667375505</v>
+        <v>0.01708716712892056</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0007270345231518149</v>
+        <v>0.01403903961181641</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.00253880163654685</v>
+        <v>0.004082862753421068</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0003447083581704646</v>
+        <v>0.009754189290106297</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0006010546931065619</v>
+        <v>0.02699635922908783</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0001746568595990539</v>
+        <v>0.01366145350039005</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.765092019923031e-05</v>
+        <v>0.02791433967649937</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0009320653043687344</v>
+        <v>0.008790932595729828</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0008338570478372276</v>
+        <v>0.01119284983724356</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0006525291246362031</v>
+        <v>0.007317361421883106</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0007007051608525217</v>
+        <v>7.058354094624519e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001597869675606489</v>
+        <v>0.0326300784945488</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0001639051188249141</v>
+        <v>0.007501693442463875</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0001114351325668395</v>
+        <v>0.01541786175221205</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001098811626434326</v>
+        <v>0.01633392460644245</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.001171701587736607</v>
+        <v>0.01589135453104973</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0004957248456776142</v>
+        <v>0.006033234298229218</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0006805744487792253</v>
+        <v>0.0002835312625393271</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0005470891483128071</v>
+        <v>0.00174060498829931</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.001384937204420567</v>
+        <v>0.00798299815505743</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.008688288740813732</v>
+        <v>0.05889663100242615</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0007976031629368663</v>
+        <v>4.497292684391141e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001491691800765693</v>
+        <v>0.02060185186564922</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.001268305815756321</v>
+        <v>0.05628785490989685</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0001012228312902153</v>
+        <v>0.007643197197467089</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0002191042149206623</v>
+        <v>0.002091090194880962</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.309964323416352e-05</v>
+        <v>0.01083081215620041</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.260190952569246e-06</v>
+        <v>0.00609462708234787</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0009330344037152827</v>
+        <v>0.0009336601942777634</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.002714635338634253</v>
+        <v>0.001389008481055498</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.002699482254683971</v>
+        <v>0.0185285210609436</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001799614634364843</v>
+        <v>0.01656338945031166</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.004897786304354668</v>
+        <v>0.005910714156925678</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001094796578399837</v>
+        <v>0.009310935623943806</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.00186398858204484</v>
+        <v>0.00874263234436512</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001248218934051692</v>
+        <v>0.01954035833477974</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.001782629755325615</v>
+        <v>0.01277580205351114</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0005686896620318294</v>
+        <v>0.003677383065223694</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.001021616975776851</v>
+        <v>0.0098619619384408</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.001278905663639307</v>
+        <v>0.001656766980886459</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0003948219818994403</v>
+        <v>0.008415184915065765</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0004068931157235056</v>
+        <v>4.29842621088028e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.001311970292590559</v>
+        <v>0.003176918253302574</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0005600566510111094</v>
+        <v>0.003083490766584873</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.28024058137089e-05</v>
+        <v>0.006451324094086885</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0002275831648148596</v>
+        <v>0.0005116192623972893</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0009897083509713411</v>
+        <v>0.00621374137699604</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.004732671193778515</v>
+        <v>0.05478192865848541</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002122142584994435</v>
+        <v>0.007177967578172684</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.002118539065122604</v>
+        <v>0.02497084811329842</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.310689347330481e-05</v>
+        <v>0.01549745071679354</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001243776874616742</v>
+        <v>0.0206395760178566</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0003994761500507593</v>
+        <v>0.01039010100066662</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0001425727677997202</v>
+        <v>0.003240225370973349</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0009221427026204765</v>
+        <v>0.01581750810146332</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.319217209238559e-05</v>
+        <v>0.0006035206606611609</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.002419843571260571</v>
+        <v>0.0327419750392437</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0008615429396741092</v>
+        <v>0.005251501686871052</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.000765484175644815</v>
+        <v>0.02627035789191723</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0004865712835453451</v>
+        <v>0.0008045135764405131</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0008154424140229821</v>
+        <v>0.003315286478027701</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0003918859001714736</v>
+        <v>0.0007306454936042428</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0001656628301134333</v>
+        <v>0.002363580511882901</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0007617772207595408</v>
+        <v>0.002832722151651978</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.00206100707873702</v>
+        <v>0.01162403542548418</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0004811772087123245</v>
+        <v>0.02966608107089996</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001610956533113495</v>
+        <v>0.0269068218767643</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0007521860534325242</v>
+        <v>0.0570002906024456</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001598554197698832</v>
+        <v>0.01557014882564545</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.001773592201061547</v>
+        <v>0.01540463324636221</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.001339538604952395</v>
+        <v>0.00480419397354126</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.002010979223996401</v>
+        <v>0.00317191774956882</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0002677743032108992</v>
+        <v>0.01027025282382965</v>
       </c>
       <c r="CV11" t="n">
-        <v>4.978617653250694e-06</v>
+        <v>0.001737499958835542</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.002145122503861785</v>
+        <v>0.03094209544360638</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.001066912547685206</v>
+        <v>0.005644770339131355</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.001163855660706758</v>
+        <v>0.02566125243902206</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0004385888169053942</v>
+        <v>0.005237201694399118</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.001142163062468171</v>
+        <v>0.003456725040450692</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0003920838353224099</v>
+        <v>0.00277462974190712</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0002056712255580351</v>
+        <v>0.001330220722593367</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0004196625377517194</v>
+        <v>0.005433329381048679</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.001044544973410666</v>
+        <v>0.004608909599483013</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.003289205022156239</v>
+        <v>0.01512219477444887</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0004143472469877452</v>
+        <v>0.003223835723474622</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.002641247818246484</v>
+        <v>0.01255106925964355</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0001630939805181697</v>
+        <v>0.02256582677364349</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.001551328809000552</v>
+        <v>0.02819820120930672</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.001670354744419456</v>
+        <v>0.00378817948512733</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.000234672668739222</v>
+        <v>0.02525058202445507</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0004234252846799791</v>
+        <v>0.01508607156574726</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.000189755650353618</v>
+        <v>0.0002103560836985707</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0007358124712482095</v>
+        <v>0.02206301689147949</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.000459983799373731</v>
+        <v>0.007950811646878719</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0003379552508704364</v>
+        <v>0.01516376622021198</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.001978120999410748</v>
+        <v>0.002397942589595914</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0006497839349322021</v>
+        <v>0.003015947295352817</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0009754211641848087</v>
+        <v>0.008908305317163467</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0005054834764450788</v>
+        <v>0.01889955811202526</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0008256395813077688</v>
+        <v>0.02687052823603153</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0002297140163136646</v>
+        <v>0.009384861215949059</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.001605753321200609</v>
+        <v>0.002006321446970105</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.000886937603354454</v>
+        <v>0.006272223312407732</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0001483146043028682</v>
+        <v>0.009046811610460281</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.001116381725296378</v>
+        <v>0.006707701832056046</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0001956317864824086</v>
+        <v>0.0191107764840126</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.00043141795322299</v>
+        <v>0.003907558042556047</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0008231549290940166</v>
+        <v>0.03843382000923157</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001058993511833251</v>
+        <v>0.02841831184923649</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0006036579143255949</v>
+        <v>0.009746921248733997</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.001484250067733228</v>
+        <v>0.02545231580734253</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0007998897926881909</v>
+        <v>0.008169458247721195</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0009854448726400733</v>
+        <v>0.0214441753923893</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.000915701559279114</v>
+        <v>0.003433274570852518</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.001675285981036723</v>
+        <v>0.002140558324754238</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0006165262311697006</v>
+        <v>0.0002334264572709799</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0003505573840811849</v>
+        <v>0.002129666972905397</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0004461602366063744</v>
+        <v>0.004074636846780777</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0003370724152773619</v>
+        <v>0.002551234094426036</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.001580799580551684</v>
+        <v>0.02742719650268555</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001371121150441468</v>
+        <v>0.0005776844918727875</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.001154986210167408</v>
+        <v>0.01618281565606594</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0001844784710556269</v>
+        <v>0.008021388202905655</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001976365922018886</v>
+        <v>0.001483992207795382</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0008987416513264179</v>
+        <v>0.009969592094421387</v>
       </c>
       <c r="EV11" t="n">
-        <v>1.060768045135774e-05</v>
+        <v>0.00586865795776248</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0007088954444043338</v>
+        <v>0.008407198823988438</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0003804689622484148</v>
+        <v>0.003150098025798798</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.002288448391482234</v>
+        <v>0.03511970490217209</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0005646419012919068</v>
+        <v>0.004246378783136606</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.001350629609078169</v>
+        <v>0.02915513515472412</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.000658850185573101</v>
+        <v>0.002740925177931786</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.00104536535218358</v>
+        <v>0.006562137976288795</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0005214405828155577</v>
+        <v>0.003443660214543343</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0001174198987428099</v>
+        <v>0.004085898399353027</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0007028821855783463</v>
+        <v>0.006337806582450867</v>
       </c>
       <c r="FG11" t="n">
-        <v>2.411282912362367e-05</v>
+        <v>0.002023397013545036</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0003330025938339531</v>
+        <v>0.01565777882933617</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0007767676142975688</v>
+        <v>0.006222465075552464</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.001278834184631705</v>
+        <v>0.01293586660176516</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0006088959635235369</v>
+        <v>0.002730529056861997</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0004717808042187244</v>
+        <v>0.004300975240767002</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0008782764198258519</v>
+        <v>0.002672300674021244</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0003126459196209908</v>
+        <v>0.005609634332358837</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0007633635541424155</v>
+        <v>0.01109282951802015</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0002626554050948471</v>
+        <v>0.01611521281301975</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.002906670095399022</v>
+        <v>0.03091191872954369</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.00109213381074369</v>
+        <v>0.00175212137401104</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.001865394879132509</v>
+        <v>0.02174502983689308</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0001716205733828247</v>
+        <v>0.009027153253555298</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0004018026520498097</v>
+        <v>0.009034356102347374</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.000154626410221681</v>
+        <v>0.007005230523645878</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0003380614798516035</v>
+        <v>0.009224267676472664</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0003942896728403866</v>
+        <v>0.01809594221413136</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.001755204168148339</v>
+        <v>0.01308195292949677</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0004106783890165389</v>
+        <v>0.02296721190214157</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0003624751116149127</v>
+        <v>0.00810273177921772</v>
       </c>
       <c r="GB11" t="n">
-        <v>1.434364730812376e-05</v>
+        <v>0.01623109728097916</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.001330737490206957</v>
+        <v>0.02331637218594551</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.001011815737001598</v>
+        <v>0.008534844033420086</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.002985119819641113</v>
+        <v>0.02173724770545959</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0001529041037429124</v>
+        <v>0.00161272194236517</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0004325065528973937</v>
+        <v>0.004739230498671532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.06575857102870941</v>
+        <v>0.0295967273414135</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8338966369628906</v>
+        <v>0.3501628637313843</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05294892191886902</v>
+        <v>0.1243953257799149</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4252380430698395</v>
+        <v>0.0314934141933918</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07336664944887161</v>
+        <v>0.07157687842845917</v>
       </c>
       <c r="F12" t="n">
-        <v>1.098012804985046</v>
+        <v>0.2173932939767838</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2480084747076035</v>
+        <v>0.02850582264363766</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3131518065929413</v>
+        <v>0.00146029144525528</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09046807885169983</v>
+        <v>0.05901223421096802</v>
       </c>
       <c r="J12" t="n">
-        <v>0.172650009393692</v>
+        <v>0.002792730927467346</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7141258716583252</v>
+        <v>0.4978576898574829</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07763016223907471</v>
+        <v>0.1327414512634277</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5661773681640625</v>
+        <v>0.09889967739582062</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1224917694926262</v>
+        <v>0.01083533465862274</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9409878849983215</v>
+        <v>0.2615796029567719</v>
       </c>
       <c r="P12" t="n">
-        <v>0.262444794178009</v>
+        <v>0.1055441796779633</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2390585392713547</v>
+        <v>0.127809002995491</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1577088832855225</v>
+        <v>0.01573896408081055</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04444761201739311</v>
+        <v>0.0869680792093277</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1336584091186523</v>
+        <v>0.09507196396589279</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04639385640621185</v>
+        <v>0.02210431732237339</v>
       </c>
       <c r="V12" t="n">
-        <v>0.07438552379608154</v>
+        <v>0.1063212603330612</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01787148416042328</v>
+        <v>0.05683938413858414</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02249258942902088</v>
+        <v>0.02268354780972004</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.005157418549060822</v>
+        <v>0.04022292792797089</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.05289885774254799</v>
+        <v>0.1675564497709274</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.01935797929763794</v>
+        <v>0.02308123186230659</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.07382475584745407</v>
+        <v>0.1100867837667465</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.08237726241350174</v>
+        <v>0.01435749232769012</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.009777231141924858</v>
+        <v>0.01519185956567526</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.02655568718910217</v>
+        <v>0.03302997723221779</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.007581315934658051</v>
+        <v>0.22092404961586</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.003197267651557922</v>
+        <v>0.1002663224935532</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.01144495606422424</v>
+        <v>0.06104512140154839</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.007671715691685677</v>
+        <v>0.1156352907419205</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.04014059156179428</v>
+        <v>0.03396286070346832</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.1234916970133781</v>
+        <v>0.03133003786206245</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.1049642786383629</v>
+        <v>0.06360211223363876</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.09678472578525543</v>
+        <v>0.003469290677458048</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0004439111799001694</v>
+        <v>0.06294190138578415</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.08183091878890991</v>
+        <v>0.03904435783624649</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.1939420402050018</v>
+        <v>0.03905559331178665</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.08923004567623138</v>
+        <v>0.05801258608698845</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.11673254519701</v>
+        <v>0.1759197562932968</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.05799339711666107</v>
+        <v>0.0391806922852993</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.04465784877538681</v>
+        <v>0.03800957649946213</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6198756098747253</v>
+        <v>0.4661482870578766</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1182066202163696</v>
+        <v>0.04725358635187149</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01735194772481918</v>
+        <v>0.01171842310577631</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03044342994689941</v>
+        <v>0.02104182541370392</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.668890118598938</v>
+        <v>0.2518218755722046</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.05624917522072792</v>
+        <v>0.02877616323530674</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.09832128882408142</v>
+        <v>0.01033447310328484</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.1059458404779434</v>
+        <v>0.04380759596824646</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.002301763743162155</v>
+        <v>0.02190801873803139</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.2477821856737137</v>
+        <v>0.01191833987832069</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.2364634126424789</v>
+        <v>0.06157052889466286</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.241421103477478</v>
+        <v>0.05162063986063004</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.1917970776557922</v>
+        <v>0.09632453322410583</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.3853176534175873</v>
+        <v>0.02260426059365273</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.08746033906936646</v>
+        <v>0.08781544864177704</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.09458056092262268</v>
+        <v>0.01831672526896</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0058872289955616</v>
+        <v>0.007917696610093117</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.01774046197533607</v>
+        <v>0.06771479547023773</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.2538631558418274</v>
+        <v>0.06367466598749161</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.02553786337375641</v>
+        <v>0.01739849895238876</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.03736945614218712</v>
+        <v>0.09009642899036407</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1676806062459946</v>
+        <v>0.06323423981666565</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.03523793071508408</v>
+        <v>0.04039476811885834</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.1628084778785706</v>
+        <v>0.02163951098918915</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.07928220927715302</v>
+        <v>0.07985654473304749</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.02630408108234406</v>
+        <v>0.04367781803011894</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.03610224649310112</v>
+        <v>0.06555177271366119</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3272297978401184</v>
+        <v>0.3000564277172089</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.01124052703380585</v>
+        <v>0.01794525235891342</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.05312877148389816</v>
+        <v>0.0768076479434967</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01364106871187687</v>
+        <v>0.03473151847720146</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.2924981713294983</v>
+        <v>0.1103694662451744</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.02539890259504318</v>
+        <v>0.0309373177587986</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.08004130423069</v>
+        <v>0.08547209948301315</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.03640299290418625</v>
+        <v>0.01621163822710514</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.007433827500790358</v>
+        <v>0.05408071726560593</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.1401144117116928</v>
+        <v>0.1017234697937965</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.03920597955584526</v>
+        <v>0.02408284693956375</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.09011198580265045</v>
+        <v>0.02363915182650089</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.06225527077913284</v>
+        <v>0.02293085306882858</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.1312504857778549</v>
+        <v>0.08000828325748444</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.04795707017183304</v>
+        <v>0.04294466599822044</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.04731075465679169</v>
+        <v>0.02877271734178066</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.03185917437076569</v>
+        <v>0.02843927405774593</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.1960085928440094</v>
+        <v>0.001415684819221497</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.1508825868368149</v>
+        <v>0.2991610467433929</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.03093691729009151</v>
+        <v>0.01138263940811157</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.05252436175942421</v>
+        <v>0.06988978385925293</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.1538019329309464</v>
+        <v>0.002309337258338928</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01052466407418251</v>
+        <v>0.1307340711355209</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.05457703769207001</v>
+        <v>0.06082800775766373</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.1084066852927208</v>
+        <v>0.01159991510212421</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.1337555944919586</v>
+        <v>0.07848578691482544</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.02719374001026154</v>
+        <v>0.036602433770895</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.1082081198692322</v>
+        <v>0.0987134575843811</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0306219570338726</v>
+        <v>0.02308487519621849</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.113532118499279</v>
+        <v>0.02769497968256474</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.02817439287900925</v>
+        <v>0.03519570827484131</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1171258091926575</v>
+        <v>0.07950267195701599</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.06031098216772079</v>
+        <v>0.01123867742717266</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.1078631579875946</v>
+        <v>0.02053001523017883</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.06676273047924042</v>
+        <v>0.03928849101066589</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.01239307224750519</v>
+        <v>0.04046236723661423</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.2960476577281952</v>
+        <v>0.06289670616388321</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.05488333851099014</v>
+        <v>0.01251744106411934</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.2121999859809875</v>
+        <v>0.0669417530298233</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1037418767809868</v>
+        <v>0.161238819360733</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.02433643862605095</v>
+        <v>0.004126179963350296</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.01756882667541504</v>
+        <v>0.09470479190349579</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2417742311954498</v>
+        <v>0.01346622966229916</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.1872466206550598</v>
+        <v>0.05191325768828392</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.04015836492180824</v>
+        <v>0.02804364077746868</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.03751147910952568</v>
+        <v>0.07043516635894775</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.09096124768257141</v>
+        <v>0.003436123952269554</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.07517556846141815</v>
+        <v>0.1166115626692772</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03612079471349716</v>
+        <v>0.08205219358205795</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06173179298639297</v>
+        <v>0.0279222447425127</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.004999792203307152</v>
+        <v>0.03451641276478767</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0216144397854805</v>
+        <v>0.1592410355806351</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.03331562131643295</v>
+        <v>0.01469241827726364</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0126240998506546</v>
+        <v>0.07832132279872894</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.07671669870615005</v>
+        <v>0.005723338108509779</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0226527526974678</v>
+        <v>0.08106577396392822</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.002227723598480225</v>
+        <v>0.02713351510465145</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.09498056024312973</v>
+        <v>0.08736193180084229</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.06056477129459381</v>
+        <v>0.1322680562734604</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.008535213768482208</v>
+        <v>0.02086658403277397</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.06850527971982956</v>
+        <v>0.03198317438364029</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0161350779235363</v>
+        <v>0.07958446443080902</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.04380499571561813</v>
+        <v>0.03867045789957047</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.05544675141572952</v>
+        <v>0.02900461480021477</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.02961210161447525</v>
+        <v>0.002753892913460732</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04532033205032349</v>
+        <v>0.03409162536263466</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.004569552838802338</v>
+        <v>0.08633090555667877</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1192740276455879</v>
+        <v>0.01639315113425255</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.04159382730722427</v>
+        <v>0.04276503622531891</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.01732873171567917</v>
+        <v>0.06401873379945755</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.05731987208127975</v>
+        <v>0.02733205258846283</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.08656676113605499</v>
+        <v>0.02572822570800781</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02458813786506653</v>
+        <v>0.01419187895953655</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.01272548735141754</v>
+        <v>0.01119647733867168</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.06262212991714478</v>
+        <v>0.08654021471738815</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0119556188583374</v>
+        <v>0.09163229167461395</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.002377201803028584</v>
+        <v>0.02477875724434853</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.06566759943962097</v>
+        <v>0.05661782622337341</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.1959791481494904</v>
+        <v>0.006269589066505432</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.04635637253522873</v>
+        <v>0.03280622512102127</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0195581242442131</v>
+        <v>0.05522317066788673</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.1018081903457642</v>
+        <v>0.1182997226715088</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.003711041063070297</v>
+        <v>0.02356959320604801</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.07071423530578613</v>
+        <v>0.02208524383604527</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001359804533421993</v>
+        <v>0.05182333290576935</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.1208581477403641</v>
+        <v>0.08147221803665161</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.08283863961696625</v>
+        <v>0.05098803341388702</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.07738390564918518</v>
+        <v>0.009216459468007088</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.02520820125937462</v>
+        <v>0.04048960655927658</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.01666545309126377</v>
+        <v>0.02600875124335289</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0695909708738327</v>
+        <v>0.1180513352155685</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.03621326759457588</v>
+        <v>0.04096759110689163</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.03832046687602997</v>
+        <v>0.1127707436680794</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.03934028744697571</v>
+        <v>0.05834369361400604</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.2235845476388931</v>
+        <v>0.03515522927045822</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.04018201306462288</v>
+        <v>0.07954154908657074</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.07312946021556854</v>
+        <v>0.1245709583163261</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0005249716341495514</v>
+        <v>0.05574361979961395</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.09479974955320358</v>
+        <v>0.03343628346920013</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.1126237511634827</v>
+        <v>0.05774383991956711</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.02018273435533047</v>
+        <v>0.00957893580198288</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.2046276926994324</v>
+        <v>0.1757777184247971</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.2121905982494354</v>
+        <v>0.001808799803256989</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.183002695441246</v>
+        <v>0.0110850790515542</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.085478276014328</v>
+        <v>0.09564016759395599</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0469113290309906</v>
+        <v>0.03251820802688599</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.03864721208810806</v>
+        <v>0.05952256172895432</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.1032835319638252</v>
+        <v>0.100206583738327</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.07257340103387833</v>
+        <v>0.034407839179039</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.06605424731969833</v>
+        <v>0.01425956841558218</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.129653126001358</v>
+        <v>0.07629943639039993</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.2489238977432251</v>
+        <v>0.003027074038982391</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.1548534631729126</v>
+        <v>0.01967634074389935</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.1235733181238174</v>
+        <v>0.03387864679098129</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.120749294757843</v>
+        <v>0.03619413450360298</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.01422047987580299</v>
+        <v>0.09897370636463165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01206095889210701</v>
+        <v>0.008886630646884441</v>
       </c>
       <c r="B13" t="n">
-        <v>0.09109248965978622</v>
+        <v>0.08719304949045181</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0103728985413909</v>
+        <v>0.006711380556225777</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04428792372345924</v>
+        <v>0.04194230958819389</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02178597263991833</v>
+        <v>0.0157685074955225</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02394033782184124</v>
+        <v>0.01800055615603924</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008214196190237999</v>
+        <v>0.01444793771952391</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00463063782081008</v>
+        <v>0.0152621790766716</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001458886545151472</v>
+        <v>0.009508154354989529</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01345566660165787</v>
+        <v>0.006682358682155609</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06831333786249161</v>
+        <v>0.09508161246776581</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004354050848633051</v>
+        <v>0.01045614387840033</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03518854454159737</v>
+        <v>0.06150022149085999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02421051263809204</v>
+        <v>0.02798807434737682</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02617909945547581</v>
+        <v>0.01133128814399242</v>
       </c>
       <c r="P13" t="n">
-        <v>0.007360587827861309</v>
+        <v>0.006872507743537426</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01554620824754238</v>
+        <v>0.01026378851383924</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001237519027199596</v>
+        <v>0.01059049181640148</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0052026123739779</v>
+        <v>0.003082208335399628</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01533466577529907</v>
+        <v>0.007593865972012281</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0006482506869360805</v>
+        <v>0.003844681661576033</v>
       </c>
       <c r="V13" t="n">
-        <v>0.01232234109193087</v>
+        <v>0.01444341242313385</v>
       </c>
       <c r="W13" t="n">
-        <v>0.007250112015753984</v>
+        <v>0.01375990267843008</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01190588064491749</v>
+        <v>0.01205448433756828</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.009756774641573429</v>
+        <v>0.008513892069458961</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01090588141232729</v>
+        <v>0.006160615477710962</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01044938899576664</v>
+        <v>0.01031664945185184</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003090864047408104</v>
+        <v>0.004887411370873451</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0007337058777920902</v>
+        <v>0.002850012853741646</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.00240844301879406</v>
+        <v>0.00659622997045517</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.000248777330853045</v>
+        <v>0.01702651381492615</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001764075830578804</v>
+        <v>0.02052470855414867</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0004118407377973199</v>
+        <v>0.01616965979337692</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.005361231975257397</v>
+        <v>0.00460678618401289</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.007291261106729507</v>
+        <v>0.01706171408295631</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.002750449348241091</v>
+        <v>0.003781924257054925</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0137910507619381</v>
+        <v>0.002795575885102153</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.008203014731407166</v>
+        <v>0.02396427094936371</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.004518687725067139</v>
+        <v>0.005375062581151724</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.008498385548591614</v>
+        <v>0.01385828852653503</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.007095917128026485</v>
+        <v>0.008412771858274937</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.007489752024412155</v>
+        <v>0.009951846674084663</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.003846562001854181</v>
+        <v>0.00337411742657423</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.005124420858919621</v>
+        <v>0.005098882596939802</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.007546397857367992</v>
+        <v>0.001949667930603027</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.000709929212462157</v>
+        <v>0.003954394720494747</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.05792265012860298</v>
+        <v>0.07582306116819382</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.00284512946382165</v>
+        <v>0.002956729149445891</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.00432521291077137</v>
+        <v>0.01397771295160055</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.003312766784802079</v>
+        <v>0.03142577037215233</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.004838784690946341</v>
+        <v>0.01156034413725138</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.005306672304868698</v>
+        <v>0.004667235072702169</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.01488570496439934</v>
+        <v>0.01071105618029833</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.00635894201695919</v>
+        <v>0.002971173264086246</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.009420977905392647</v>
+        <v>0.003774504642933607</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01211782358586788</v>
+        <v>0.003630834631621838</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01811728253960609</v>
+        <v>0.01148682739585638</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.01235800143331289</v>
+        <v>0.009663260541856289</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03437091037631035</v>
+        <v>0.001692484365776181</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.007426565978676081</v>
+        <v>0.00653769401833415</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.003949720878154039</v>
+        <v>0.002317091450095177</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0148693285882473</v>
+        <v>0.01166138611733913</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0009880184661597013</v>
+        <v>0.008357095532119274</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01059270370751619</v>
+        <v>0.002254076534882188</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.01168635115027428</v>
+        <v>0.00224823784083128</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.004893748555332422</v>
+        <v>0.0008134718518704176</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.003052592743188143</v>
+        <v>0.001461419742554426</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.007972307503223419</v>
+        <v>0.01165420189499855</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.006972644943743944</v>
+        <v>0.003837360301986337</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.00289008067920804</v>
+        <v>0.01735077612102032</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.006829544436186552</v>
+        <v>1.216941745951772e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.004396851174533367</v>
+        <v>0.0008997716940939426</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.001272907247766852</v>
+        <v>0.001996036851778626</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03084861859679222</v>
+        <v>0.04730500653386116</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.009500628337264061</v>
+        <v>0.002508445177227259</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.003931665327399969</v>
+        <v>0.02251315861940384</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.000475649198051542</v>
+        <v>0.006951671559363604</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.006719714496284723</v>
+        <v>0.01475094258785248</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.009506498463451862</v>
+        <v>0.0107945566996932</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.00149294501170516</v>
+        <v>0.003086854238063097</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.003885478479787707</v>
+        <v>0.009131168015301228</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002172754611819983</v>
+        <v>0.000476415385492146</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01442501880228519</v>
+        <v>0.02868697047233582</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.006965266540646553</v>
+        <v>0.002887884620577097</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.004844359587877989</v>
+        <v>0.01299665682017803</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.00435128528624773</v>
+        <v>0.004104740917682648</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.006044243928045034</v>
+        <v>0.003396275220438838</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.003854217939078808</v>
+        <v>0.00208723871037364</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.003790640737861395</v>
+        <v>0.001896129222586751</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.005592984613031149</v>
+        <v>0.00106619915459305</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01388347242027521</v>
+        <v>0.01697725616395473</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0007932994049042463</v>
+        <v>0.03864963352680206</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.005570509936660528</v>
+        <v>0.01995576173067093</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01465542800724506</v>
+        <v>0.03400484472513199</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01335102785378695</v>
+        <v>0.003948357421904802</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.01241196971386671</v>
+        <v>0.0126236705109477</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.01111125946044922</v>
+        <v>0.005509762093424797</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.003109805285930634</v>
+        <v>0.0002811517915688455</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.008289970457553864</v>
+        <v>0.00153850787319243</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0003277172509115189</v>
+        <v>0.002875756705179811</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01363167259842157</v>
+        <v>0.02709127590060234</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.005967275239527225</v>
+        <v>0.003525767009705305</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.007835098542273045</v>
+        <v>0.01424687262624502</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005319413729012012</v>
+        <v>0.004128172062337399</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.006810033693909645</v>
+        <v>0.004111199639737606</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.005198796279728413</v>
+        <v>0.0008531725616194308</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.005456472281366587</v>
+        <v>0.001938597299158573</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.003689792472869158</v>
+        <v>0.00262292311526835</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.005795667879283428</v>
+        <v>0.007980612106621265</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01313889399170876</v>
+        <v>0.01466772891581059</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.01181857753545046</v>
+        <v>0.002974230330437422</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.02904278971254826</v>
+        <v>0.01482463255524635</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.006863774266093969</v>
+        <v>0.02124815993010998</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.007724453695118427</v>
+        <v>0.01750538684427738</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.002825801726430655</v>
+        <v>0.007951529696583748</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.00192351033911109</v>
+        <v>0.01830521039664745</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.00557427667081356</v>
+        <v>0.005377446766942739</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.007083493284881115</v>
+        <v>0.0009978929301723838</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.004092266783118248</v>
+        <v>0.01309845969080925</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.00167722231708467</v>
+        <v>0.001720796572044492</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.004007133189588785</v>
+        <v>0.002676640171557665</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.006166164297610521</v>
+        <v>0.0003134043654426932</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.006029566749930382</v>
+        <v>0.001147427246905863</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.005637085065245628</v>
+        <v>0.007884373888373375</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.003538434859365225</v>
+        <v>0.01154784392565489</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.008514180779457092</v>
+        <v>0.01168136671185493</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0042829979211092</v>
+        <v>0.008451439440250397</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.003511090064421296</v>
+        <v>0.0104650380089879</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.01422491483390331</v>
+        <v>0.008717643097043037</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.001357648521661758</v>
+        <v>0.01336507592350245</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.008128060959279537</v>
+        <v>0.005262371152639389</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.005015063099563122</v>
+        <v>0.01139888819307089</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.002397234318777919</v>
+        <v>0.0002136636758223176</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.001328210346400738</v>
+        <v>0.02360985241830349</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.00532271945849061</v>
+        <v>0.01563564315438271</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0102662704885006</v>
+        <v>0.006035011261701584</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01377177983522415</v>
+        <v>0.01615298166871071</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.005483993329107761</v>
+        <v>0.006232165265828371</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.004168950021266937</v>
+        <v>0.008541816845536232</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002843505935743451</v>
+        <v>0.00524151511490345</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.00559732411056757</v>
+        <v>0.00170859124045819</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.007089343853294849</v>
+        <v>0.001064528245478868</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.001270719105377793</v>
+        <v>0.0009315048810094595</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.001990661956369877</v>
+        <v>0.002987400162965059</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0007277142722159624</v>
+        <v>0.002561438595876098</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.006206242367625237</v>
+        <v>0.01848864555358887</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.005037328228354454</v>
+        <v>0.0002486289013177156</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.003112999722361565</v>
+        <v>0.01005208864808083</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.005586758255958557</v>
+        <v>0.002701799385249615</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01008878462016582</v>
+        <v>0.001194439828395844</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.009542716667056084</v>
+        <v>0.005459953565150499</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0112857474014163</v>
+        <v>0.005233305040746927</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.006479622796177864</v>
+        <v>0.008939526043832302</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001151663716882467</v>
+        <v>0.0006849735509604216</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0133225079625845</v>
+        <v>0.03105275332927704</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.004397907759994268</v>
+        <v>0.002314343117177486</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.006177911069244146</v>
+        <v>0.01631499081850052</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003743528155609965</v>
+        <v>0.001837702700868249</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.005521371029317379</v>
+        <v>0.004880469758063555</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.00580659182742238</v>
+        <v>0.003971944563090801</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.003646144177764654</v>
+        <v>0.004353971220552921</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.006530437152832747</v>
+        <v>0.00428246334195137</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.005909050814807415</v>
+        <v>0.001345299882814288</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.006837671622633934</v>
+        <v>0.01344344019889832</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.007972369901835918</v>
+        <v>0.003659726586192846</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01212129835039377</v>
+        <v>0.01011762861162424</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.007665920536965132</v>
+        <v>0.002623276319354773</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.004915529862046242</v>
+        <v>0.000784767500590533</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.006827594246715307</v>
+        <v>0.006101162172853947</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.006592946127057076</v>
+        <v>0.001240797806531191</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.00501698162406683</v>
+        <v>0.0005992306396365166</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001383577240630984</v>
+        <v>0.006687828805297613</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.006801934447139502</v>
+        <v>0.02712282165884972</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.007514047902077436</v>
+        <v>0.008978890255093575</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.003944656811654568</v>
+        <v>0.01703909039497375</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.009308093227446079</v>
+        <v>0.002110985573381186</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.004338014405220747</v>
+        <v>0.005557846277952194</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001353535801172256</v>
+        <v>0.0002151420339941978</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.002810160862281919</v>
+        <v>0.002186957513913512</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.008812081068754196</v>
+        <v>0.009783659130334854</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0133697846904397</v>
+        <v>0.004693928174674511</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.004076543729752302</v>
+        <v>0.01536745857447386</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.001819008612073958</v>
+        <v>0.004989412613213062</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.001006625592708588</v>
+        <v>0.01628962531685829</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.00368634145706892</v>
+        <v>0.00948004238307476</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.007235222496092319</v>
+        <v>0.009599406272172928</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.02175240404903889</v>
+        <v>0.02070673927664757</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.005577054806053638</v>
+        <v>0.007738831918686628</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.01110307686030865</v>
+        <v>0.001116414554417133</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.00605520186945796</v>
+        <v>0.04197480529546738</v>
       </c>
       <c r="B14" t="n">
-        <v>0.07111711055040359</v>
+        <v>0.1153412535786629</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003004972590133548</v>
+        <v>0.005549169611185789</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04241321608424187</v>
+        <v>0.009100867435336113</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02354795671999454</v>
+        <v>0.03291487321257591</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09279944002628326</v>
+        <v>0.1520613133907318</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0007006078958511353</v>
+        <v>0.01015191711485386</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0456116572022438</v>
+        <v>0.1014134138822556</v>
       </c>
       <c r="I14" t="n">
-        <v>0.006559393368661404</v>
+        <v>0.008097116835415363</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01819384098052979</v>
+        <v>0.02093956619501114</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06220272555947304</v>
+        <v>0.1471177339553833</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005882679019123316</v>
+        <v>0.02708132378757</v>
       </c>
       <c r="M14" t="n">
-        <v>0.03168440237641335</v>
+        <v>0.05193682014942169</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01343173999339342</v>
+        <v>0.07183259725570679</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09082676470279694</v>
+        <v>0.1661133468151093</v>
       </c>
       <c r="P14" t="n">
-        <v>0.001725750043988228</v>
+        <v>0.0167769081890583</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02369652129709721</v>
+        <v>0.05283355712890625</v>
       </c>
       <c r="R14" t="n">
-        <v>0.003489743918180466</v>
+        <v>0.01111604645848274</v>
       </c>
       <c r="S14" t="n">
-        <v>0.003972571808844805</v>
+        <v>0.01013158913701773</v>
       </c>
       <c r="T14" t="n">
-        <v>0.004146374762058258</v>
+        <v>0.05452405288815498</v>
       </c>
       <c r="U14" t="n">
-        <v>0.006603076122701168</v>
+        <v>0.005176889710128307</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01090054865926504</v>
+        <v>0.062225591391325</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01517199072986841</v>
+        <v>0.04046208783984184</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01057664584368467</v>
+        <v>0.01858278177678585</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.00880656111985445</v>
+        <v>0.009428816847503185</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.008946099318563938</v>
+        <v>0.03456391394138336</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.009955420158803463</v>
+        <v>0.007079911418259144</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.004339603707194328</v>
+        <v>0.007119810208678246</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.004715758375823498</v>
+        <v>0.02262143604457378</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.007002281956374645</v>
+        <v>0.0006077733123674989</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0006738591473549604</v>
+        <v>0.07111597061157227</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.006307448726147413</v>
+        <v>0.1144400984048843</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.008228148333728313</v>
+        <v>0.03239190950989723</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.001540383556857705</v>
+        <v>0.0114267747849226</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.008307682350277901</v>
+        <v>0.08410999178886414</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0007116454653441906</v>
+        <v>0.01890888996422291</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.009851602837443352</v>
+        <v>0.002103799022734165</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01001841388642788</v>
+        <v>0.06665368378162384</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0008608037605881691</v>
+        <v>0.01149553712457418</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.004553984384983778</v>
+        <v>0.006368224043399096</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.005768503062427044</v>
+        <v>0.04344560205936432</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0103003578260541</v>
+        <v>0.04843086004257202</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0006049014627933502</v>
+        <v>0.03289440274238586</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.008232093416154385</v>
+        <v>0.05557852983474731</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.005467869341373444</v>
+        <v>0.0169878825545311</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.003624787321314216</v>
+        <v>0.01665311865508556</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.04615496471524239</v>
+        <v>0.2678660750389099</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.003870685584843159</v>
+        <v>0.002529657445847988</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.01378447189927101</v>
+        <v>0.002581730950623751</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.006629946641623974</v>
+        <v>0.0004921108484268188</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.04849285259842873</v>
+        <v>0.1059373617172241</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.002285039983689785</v>
+        <v>0.007830403745174408</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.01814816519618034</v>
+        <v>3.921450115740299e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.01074428297579288</v>
+        <v>0.006782462354749441</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.006256901659071445</v>
+        <v>0.03061892464756966</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.01541064772754908</v>
+        <v>0.09275221824645996</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.02084417827427387</v>
+        <v>0.007972341030836105</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.01494728401303291</v>
+        <v>0.03557850793004036</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.021289287135005</v>
+        <v>0.07961342483758926</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.02260342240333557</v>
+        <v>0.006730476394295692</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.001755330711603165</v>
+        <v>0.02672312967479229</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.002037791069597006</v>
+        <v>0.03165283426642418</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.003097969107329845</v>
+        <v>0.0004190360195934772</v>
       </c>
       <c r="BL14" t="n">
-        <v>8.054543286561966e-05</v>
+        <v>0.01293718907982111</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.02007756568491459</v>
+        <v>0.03627024590969086</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.002811155747622252</v>
+        <v>0.02350075356662273</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.01126546133309603</v>
+        <v>0.01309245824813843</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.00422744220122695</v>
+        <v>0.04129999503493309</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.000397734169382602</v>
+        <v>0.003676136024296284</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001557913143187761</v>
+        <v>0.07907543331384659</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0003083990886807442</v>
+        <v>0.02120796404778957</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0003693010658025742</v>
+        <v>0.02305988781154156</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.003379610367119312</v>
+        <v>0.03096005506813526</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.02606438659131527</v>
+        <v>0.1466545462608337</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.004629245959222317</v>
+        <v>0.003217691089957952</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01250831596553326</v>
+        <v>0.0118749663233757</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.00706399604678154</v>
+        <v>0.0265220757573843</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.03238828107714653</v>
+        <v>0.08813393115997314</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.006001325324177742</v>
+        <v>0.02223947271704674</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.01100552640855312</v>
+        <v>0.02052678726613522</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.005680672358721495</v>
+        <v>0.0145472539588809</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.001724930363707244</v>
+        <v>0.000494060106575489</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.00981336273252964</v>
+        <v>0.04852604120969772</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.008755505084991455</v>
+        <v>0.009211412630975246</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.00733715295791626</v>
+        <v>0.009212550707161427</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.004246060270816088</v>
+        <v>0.01951586455106735</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01788116805255413</v>
+        <v>0.04799623042345047</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.005294790491461754</v>
+        <v>0.02530973218381405</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.006869924254715443</v>
+        <v>0.01854357123374939</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.004530639387667179</v>
+        <v>0.005676933098584414</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.009061673656105995</v>
+        <v>0.05774150043725967</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.002511260332539678</v>
+        <v>0.1162616387009621</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.002219727728515863</v>
+        <v>0.01345242373645306</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.001912951935082674</v>
+        <v>0.06945344805717468</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.00498613016679883</v>
+        <v>0.09549671411514282</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.007427274715155363</v>
+        <v>0.06614825129508972</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.01099291630089283</v>
+        <v>0.01086531765758991</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0133527209982276</v>
+        <v>0.01626951619982719</v>
       </c>
       <c r="CU14" t="n">
-        <v>7.108441786840558e-05</v>
+        <v>0.004879401065409184</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0002151514054276049</v>
+        <v>0.01306634955108166</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.00768456282094121</v>
+        <v>0.03811724856495857</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.008062686771154404</v>
+        <v>0.008454852737486362</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.01092622149735689</v>
+        <v>0.004897791892290115</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.002570623299106956</v>
+        <v>0.01868641190230846</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.01922774873673916</v>
+        <v>0.04799738898873329</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.004043932072818279</v>
+        <v>0.008923408575356007</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.01060015242546797</v>
+        <v>0.01757668703794479</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0001493059098720551</v>
+        <v>0.002464041346684098</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.005592879373580217</v>
+        <v>0.05368860438466072</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003414056729525328</v>
+        <v>0.01856316812336445</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.00477557722479105</v>
+        <v>0.01044779270887375</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.03524743393063545</v>
+        <v>0.01529256999492645</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.007785850204527378</v>
+        <v>0.06856665760278702</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0009349151514470577</v>
+        <v>0.01215878780931234</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.004661714192479849</v>
+        <v>0.02321502938866615</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.01843022741377354</v>
+        <v>0.01013673562556505</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.009370164014399052</v>
+        <v>0.05282531678676605</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0006741489050909877</v>
+        <v>0.0001983626279979944</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.002201472176238894</v>
+        <v>0.03791434690356255</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.007165747229009867</v>
+        <v>0.005151801276952028</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.001076743006706238</v>
+        <v>0.04171869158744812</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.006861348170787096</v>
+        <v>0.0152459479868412</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.009305737912654877</v>
+        <v>0.01386171486228704</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.01465499401092529</v>
+        <v>0.007170316763222218</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.009712766855955124</v>
+        <v>0.04075393080711365</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.006862504873424768</v>
+        <v>0.004495784640312195</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.001073208171874285</v>
+        <v>0.005981376394629478</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.002319824416190386</v>
+        <v>0.01772552169859409</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.01183941308408976</v>
+        <v>0.01290254108607769</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001509353518486023</v>
+        <v>0.01872453093528748</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.003625744953751564</v>
+        <v>0.0267799124121666</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.008922336623072624</v>
+        <v>0.02209634333848953</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.00133106205612421</v>
+        <v>0.004680556710809469</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.004525057040154934</v>
+        <v>0.00205958541482687</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.002731823362410069</v>
+        <v>0.007366751320660114</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.00575572345405817</v>
+        <v>0.01702559366822243</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.009253531694412231</v>
+        <v>0.01851410791277885</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.008288519456982613</v>
+        <v>0.01094838418066502</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0004415526054799557</v>
+        <v>0.03628054261207581</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.003096663858741522</v>
+        <v>0.01564781367778778</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.01684578135609627</v>
+        <v>0.02051779255270958</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.005216921214014292</v>
+        <v>0.0009474977850914001</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.003250750247389078</v>
+        <v>0.01724201440811157</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0005514324875548482</v>
+        <v>0.01222964376211166</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.001486499444581568</v>
+        <v>0.001628783531486988</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001952224294655025</v>
+        <v>0.0200309082865715</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.001134876627475023</v>
+        <v>0.007236365228891373</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.003347649006173015</v>
+        <v>0.02827154844999313</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0003602064680308104</v>
+        <v>0.01368026342242956</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.007651521358639002</v>
+        <v>0.02683717384934425</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.001497975550591946</v>
+        <v>0.03108843788504601</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.02671957388520241</v>
+        <v>0.00513688288629055</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.007956605404615402</v>
+        <v>0.005185571499168873</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0004537884960882366</v>
+        <v>0.006540484260767698</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.006299460772424936</v>
+        <v>0.05039266496896744</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.00541710015386343</v>
+        <v>0.0129495607689023</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.01011752896010876</v>
+        <v>0.003783485852181911</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.003882639110088348</v>
+        <v>0.01700019650161266</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.01657954417169094</v>
+        <v>0.04715986922383308</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.007062651682645082</v>
+        <v>0.02222063578665257</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.006550000980496407</v>
+        <v>0.01993421837687492</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.003273742273449898</v>
+        <v>0.002707874402403831</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.003479471895843744</v>
+        <v>0.02594494447112083</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.006586012896150351</v>
+        <v>0.05791508406400681</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.005987388081848621</v>
+        <v>0.00374371325597167</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.01997215300798416</v>
+        <v>0.05467002838850021</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.002293068915605545</v>
+        <v>0.01760575175285339</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.007563839666545391</v>
+        <v>0.05187469720840454</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.003190956311300397</v>
+        <v>0.02773668058216572</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.002799129579216242</v>
+        <v>0.07724494487047195</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.006272230762988329</v>
+        <v>0.007469616830348969</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.008615442551672459</v>
+        <v>0.006310857832431793</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.01226801797747612</v>
+        <v>0.05566250532865524</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.005249871406704187</v>
+        <v>0.01993172988295555</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.01939520984888077</v>
+        <v>0.06513754278421402</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.009408886544406414</v>
+        <v>0.04653634130954742</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.009016778320074081</v>
+        <v>0.09265661239624023</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.003522311570122838</v>
+        <v>0.0225102137774229</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.004928651265799999</v>
+        <v>0.01193482149392366</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.008423935621976852</v>
+        <v>0.01156149804592133</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0132762948051095</v>
+        <v>0.01575546152889729</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.00669210497289896</v>
+        <v>0.01039171777665615</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.007452181074768305</v>
+        <v>0.03522223606705666</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.005016274284571409</v>
+        <v>0.03060628846287727</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.01234840601682663</v>
+        <v>0.01438625250011683</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.002573397941887379</v>
+        <v>0.007382594048976898</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.03399992361664772</v>
+        <v>0.01928619295358658</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.006381338462233543</v>
+        <v>0.03687861561775208</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.005575570277869701</v>
+        <v>0.01666738092899323</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.00204048864543438</v>
+        <v>0.007901977747678757</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02313845045864582</v>
+        <v>0.02896992862224579</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0003172686265315861</v>
+        <v>0.008783189579844475</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01797297969460487</v>
+        <v>0.007015752606093884</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00418649148195982</v>
+        <v>0.007607481442391872</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004857760388404131</v>
+        <v>0.006861791480332613</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002304533030837774</v>
+        <v>0.009833516553044319</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004099972080439329</v>
+        <v>0.008241757750511169</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0011614840477705</v>
+        <v>0.008554537780582905</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0007797430735081434</v>
+        <v>0.006336529739201069</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02189173176884651</v>
+        <v>0.03692744672298431</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001978922635316849</v>
+        <v>0.0101922582834959</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01560214348137379</v>
+        <v>0.01771515049040318</v>
       </c>
       <c r="N15" t="n">
-        <v>0.006255005020648241</v>
+        <v>0.0121775921434164</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001794697367586195</v>
+        <v>0.0003449057694524527</v>
       </c>
       <c r="P15" t="n">
-        <v>0.001185495057143271</v>
+        <v>0.002130133798345923</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.00322849047370255</v>
+        <v>0.002628015587106347</v>
       </c>
       <c r="R15" t="n">
-        <v>0.001944284420460463</v>
+        <v>0.01161080226302147</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001649635145440698</v>
+        <v>0.00193215417675674</v>
       </c>
       <c r="T15" t="n">
-        <v>0.004376377444714308</v>
+        <v>0.003516614902764559</v>
       </c>
       <c r="U15" t="n">
-        <v>1.296593109145761e-05</v>
+        <v>0.000769477803260088</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0007236648816615343</v>
+        <v>0.002503125462681055</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001223614206537604</v>
+        <v>9.179546032100916e-05</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0002399843506282195</v>
+        <v>0.00234528910368681</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002316733356565237</v>
+        <v>0.004061487503349781</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.003333220491185784</v>
+        <v>0.0003575969894882292</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.003583193989470601</v>
+        <v>0.002604465000331402</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0004844078794121742</v>
+        <v>0.0004721703007817268</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.00504347775131464</v>
+        <v>0.004815362393856049</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0009770197793841362</v>
+        <v>0.002593554090708494</v>
       </c>
       <c r="AE15" t="n">
-        <v>6.979249883443117e-05</v>
+        <v>0.008336880244314671</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001538332435302436</v>
+        <v>0.003401427529752254</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.002275535138323903</v>
+        <v>0.005596320144832134</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.002107339445501566</v>
+        <v>0.001845127437263727</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0007809916278347373</v>
+        <v>0.01127067767083645</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0008483229903504252</v>
+        <v>0.001384945120662451</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.001271125394850969</v>
+        <v>0.002631925977766514</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.002656278200447559</v>
+        <v>0.006474048364907503</v>
       </c>
       <c r="AM15" t="n">
-        <v>9.462748130317777e-05</v>
+        <v>0.00379868084564805</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.001967964228242636</v>
+        <v>0.0001259569689864293</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.003588306251913309</v>
+        <v>0.0004332414246164262</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.001651891972869635</v>
+        <v>0.004980169702321291</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.003026031889021397</v>
+        <v>0.002986895386129618</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.001042600139044225</v>
+        <v>0.00532581890001893</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.315245966310613e-06</v>
+        <v>0.002085008192807436</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.003962119575589895</v>
+        <v>0.00283021992072463</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.01820545271039009</v>
+        <v>0.03211218863725662</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.004280108027160168</v>
+        <v>0.002927067689597607</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.004767477046698332</v>
+        <v>0.001681424444541335</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.001690026256255805</v>
+        <v>0.01257795561105013</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.001607106067240238</v>
+        <v>0.007336042355746031</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.000835749669931829</v>
+        <v>0.001808147178962827</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.002652955474331975</v>
+        <v>0.001472496194764972</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.000784540839958936</v>
+        <v>0.001142696943134069</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.004346685484051704</v>
+        <v>0.001985636074095964</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.001409901073202491</v>
+        <v>0.005250534974038601</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.004118717741221189</v>
+        <v>0.005042251665145159</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.002521950285881758</v>
+        <v>0.004519863985478878</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.004878808278590441</v>
+        <v>0.0007456514285877347</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.002219323301687837</v>
+        <v>0.006709928624331951</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0003115875297226012</v>
+        <v>0.005492205265909433</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.005276320036500692</v>
+        <v>0.00608396902680397</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0009241763618774712</v>
+        <v>0.007803457789123058</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.003303064033389091</v>
+        <v>0.0009370802436023951</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.003601133590564132</v>
+        <v>0.006297762505710125</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.000812167301774025</v>
+        <v>0.003395322943106294</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.001400201348587871</v>
+        <v>0.001276274328120053</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.006390348076820374</v>
+        <v>0.007751591503620148</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.001624531578272581</v>
+        <v>3.141927300021052e-05</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0008918547537177801</v>
+        <v>0.008975474163889885</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.002177475253120065</v>
+        <v>0.0014021135866642</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.003005301347002387</v>
+        <v>0.0003280295059084892</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.001769402646459639</v>
+        <v>0.0003538300516083837</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.008787378668785095</v>
+        <v>0.01780226454138756</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.0009435181273147464</v>
+        <v>0.00390003714710474</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.00227796658873558</v>
+        <v>0.005416445899754763</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.002287188544869423</v>
+        <v>0.0005929389735683799</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.001066923490725458</v>
+        <v>0.001213134964928031</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.002042550593614578</v>
+        <v>0.00527005922049284</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0003235331387259066</v>
+        <v>0.001589488936588168</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.002256168751046062</v>
+        <v>0.000324516964610666</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0001367096410831437</v>
+        <v>0.0006151085253804922</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.00415341230109334</v>
+        <v>0.00937504880130291</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.000757418223656714</v>
+        <v>0.003523825434967875</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.001342139556072652</v>
+        <v>0.00152884132694453</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0008384785032831132</v>
+        <v>0.001826400519348681</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.001041678595356643</v>
+        <v>0.0003854287497233599</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0007302277954295278</v>
+        <v>0.0005363774253055453</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0004036806058138609</v>
+        <v>0.001778739970177412</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0006595211452804506</v>
+        <v>0.001036160392686725</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.007866551168262959</v>
+        <v>0.009668410755693913</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.002631722018122673</v>
+        <v>0.01574802026152611</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0005324726807884872</v>
+        <v>0.006645744666457176</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.007683404255658388</v>
+        <v>0.008749064989387989</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.006520234048366547</v>
+        <v>0.0007601643446832895</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.002453233581036329</v>
+        <v>0.004136946052312851</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.005337046459317207</v>
+        <v>0.003122077323496342</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.006777374073863029</v>
+        <v>0.0004774872213602066</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0001625257427804172</v>
+        <v>0.0002251378609798849</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0006719677476212382</v>
+        <v>0.00220413925126195</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.003747478593140841</v>
+        <v>0.008796005509793758</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.001650928636081517</v>
+        <v>0.002780995797365904</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.002883469220250845</v>
+        <v>0.003160496242344379</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.00101289851590991</v>
+        <v>0.0003163993824273348</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0007101313094608486</v>
+        <v>0.0009578070603311062</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.001373455277644098</v>
+        <v>0.0008108147885650396</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.0008911755285225809</v>
+        <v>0.0009404824231751263</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.43313518492505e-05</v>
+        <v>0.002547406358644366</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.002848365344107151</v>
+        <v>0.004244223237037659</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0002124615712091327</v>
+        <v>0.001642233808524907</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.002175802597776055</v>
+        <v>0.0003652652376331389</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.003859329503029585</v>
+        <v>0.005666684824973345</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.001017273752950132</v>
+        <v>0.01065747812390327</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.000132251821924001</v>
+        <v>0.01232967805117369</v>
       </c>
       <c r="DK15" t="n">
-        <v>9.033136302605271e-05</v>
+        <v>0.001600661082193255</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.001581138232722878</v>
+        <v>0.003687581978738308</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0008922094712033868</v>
+        <v>0.0005543580045923591</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.0001144923735409975</v>
+        <v>0.00508349621668458</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0008948990143835545</v>
+        <v>0.007326429709792137</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.002163309836760163</v>
+        <v>0.0001909505517687649</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.003058963920921087</v>
+        <v>0.007529118098318577</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0026127805467695</v>
+        <v>0.002224096795544028</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0003030444495379925</v>
+        <v>0.0007007102249190211</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.0002397216885583475</v>
+        <v>0.0005747432005591691</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.001693193567916751</v>
+        <v>0.004522249568253756</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.002220205496996641</v>
+        <v>0.0007533752359449863</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.001370731508359313</v>
+        <v>0.003081298898905516</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.002397410338744521</v>
+        <v>0.003820273326709867</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.003006635466590524</v>
+        <v>0.002729982137680054</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.00113787455484271</v>
+        <v>2.99219973385334e-05</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0002005323767662048</v>
+        <v>0.003898854833096266</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0006766590522602201</v>
+        <v>0.0004736619594041258</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.001775635057128966</v>
+        <v>0.002357505727559328</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.001838086755014956</v>
+        <v>0.01135235652327538</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0003064034390263259</v>
+        <v>0.005601642187684774</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0003260623198002577</v>
+        <v>4.506082041189075e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.002853359561413527</v>
+        <v>0.003287992905825377</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.001727991853840649</v>
+        <v>0.0007470916025340557</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.002923561492934823</v>
+        <v>0.009294695220887661</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.004314104560762644</v>
+        <v>0.0002158963470719755</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0006429659551940858</v>
+        <v>0.001783218118362129</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.0007120741065591574</v>
+        <v>3.728902811417356e-06</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0003352649218868464</v>
+        <v>0.0003989003598690033</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.000991866341792047</v>
+        <v>0.003400234272703528</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.0001455578021705151</v>
+        <v>0.002552471589297056</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.004483310971409082</v>
+        <v>0.00219567702151835</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.001940592541359365</v>
+        <v>0.003792584873735905</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.001703193527646363</v>
+        <v>0.0004000483313575387</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0004354188276920468</v>
+        <v>0.00113315018825233</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.001288429019041359</v>
+        <v>0.004433632828295231</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.003264273516833782</v>
+        <v>3.021055636054371e-05</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.003816842334344983</v>
+        <v>0.0009659356437623501</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.003081798320636153</v>
+        <v>0.001648278092034161</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.00043765630107373</v>
+        <v>0.001068843645043671</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.003891615197062492</v>
+        <v>0.01126475818455219</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001036220928654075</v>
+        <v>0.002394148148596287</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.001959110843017697</v>
+        <v>0.003305122721940279</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.000440368487033993</v>
+        <v>0.0009535655844956636</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0004508529091253877</v>
+        <v>0.0003840842109639198</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.001158581348136067</v>
+        <v>0.001164570450782776</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0003384279843885452</v>
+        <v>0.001426210394129157</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0004746599588543177</v>
+        <v>0.001999314874410629</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0002963683800771832</v>
+        <v>0.001623428077436984</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.001575548434630036</v>
+        <v>0.006176704075187445</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.005161426961421967</v>
+        <v>0.0006331149488687515</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.002566083334386349</v>
+        <v>0.006054509431123734</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.001360972877591848</v>
+        <v>0.0008722285274416208</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0008491107728332281</v>
+        <v>0.003298553405329585</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.001023632124997675</v>
+        <v>0.001520027755759656</v>
       </c>
       <c r="FN15" t="n">
-        <v>3.768735041376203e-05</v>
+        <v>0.0003083834890276194</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.0008881108369678259</v>
+        <v>0.00245251227170229</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.00264901015907526</v>
+        <v>0.004596369806677103</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.001097355154342949</v>
+        <v>0.005874183960258961</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.004944325890392065</v>
+        <v>0.002675325144082308</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.002175896428525448</v>
+        <v>0.000173116335645318</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.003253344213590026</v>
+        <v>0.01230031903833151</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.002657542005181313</v>
+        <v>0.005390177015215158</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.00125755462795496</v>
+        <v>3.688689321279526e-05</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.0004856179875787348</v>
+        <v>0.004532902501523495</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.001518592122010887</v>
+        <v>5.417619831860065e-05</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.004361808300018311</v>
+        <v>0.0008955072844401002</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.001484389184042811</v>
+        <v>0.003472336800768971</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.002144872676581144</v>
+        <v>0.003030025865882635</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.001455323421396315</v>
+        <v>0.001795383752323687</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.0007801305036991835</v>
+        <v>0.001137879560701549</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.003843984566628933</v>
+        <v>0.003903171280398965</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.009056613780558109</v>
+        <v>0.00466953357681632</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.001379546825774014</v>
+        <v>0.005676089320331812</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.002989866537973285</v>
+        <v>0.001470284070819616</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.008470552042126656</v>
+        <v>0.0005411801976151764</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2703885734081268</v>
+        <v>0.00329734617844224</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1138880401849747</v>
+        <v>0.001103791641071439</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02686166949570179</v>
+        <v>0.001114423619583249</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06162579730153084</v>
+        <v>5.327101098373532e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03449483588337898</v>
+        <v>0.001320456387475133</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02684349566698074</v>
+        <v>5.779805360361934e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.006958406418561935</v>
+        <v>3.319329698570073e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0166374184191227</v>
+        <v>0.00202141422778368</v>
       </c>
       <c r="J16" t="n">
-        <v>0.04037036374211311</v>
+        <v>0.000478774105431512</v>
       </c>
       <c r="K16" t="n">
-        <v>0.219831794500351</v>
+        <v>0.003956052474677563</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07793748378753662</v>
+        <v>0.001213661627843976</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04635576158761978</v>
+        <v>0.001848586020059884</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04302459955215454</v>
+        <v>0.0008522943244315684</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02403596043586731</v>
+        <v>0.001627991441637278</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01486489363014698</v>
+        <v>0.0002210634993389249</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0454489067196846</v>
+        <v>0.000829509284812957</v>
       </c>
       <c r="R16" t="n">
-        <v>0.02275429852306843</v>
+        <v>0.001477954559959471</v>
       </c>
       <c r="S16" t="n">
-        <v>0.006174187175929546</v>
+        <v>0.0002137176197720692</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02243567258119583</v>
+        <v>0.0002564651367720217</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01037906855344772</v>
+        <v>0.0004477453185245395</v>
       </c>
       <c r="V16" t="n">
-        <v>0.009536942467093468</v>
+        <v>0.0001977374486159533</v>
       </c>
       <c r="W16" t="n">
-        <v>0.001562380231916904</v>
+        <v>0.0001690960634732619</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02150831930339336</v>
+        <v>0.0002790338767226785</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0005898196250200272</v>
+        <v>0.0001163807610282674</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.05728831887245178</v>
+        <v>0.0004546694399323314</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.01155564468353987</v>
+        <v>0.001118652638979256</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.003654682077467442</v>
+        <v>0.0009839989943429828</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.04582299292087555</v>
+        <v>0.0001124513000831939</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.01182537898421288</v>
+        <v>0.000314928765874356</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0005629216320812702</v>
+        <v>0.001262611011043191</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0194521751254797</v>
+        <v>0.0006627261755056679</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.001566577702760696</v>
+        <v>0.0004154399503022432</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.01965050026774406</v>
+        <v>0.0007996698259375989</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.02145804092288017</v>
+        <v>0.0006623509107157588</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01619178615510464</v>
+        <v>0.00064641929930076</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.04029420763254166</v>
+        <v>0.0003427086630836129</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.01915897242724895</v>
+        <v>0.0007247222238220274</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.03371468931436539</v>
+        <v>1.340488961432129e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.003912846557796001</v>
+        <v>1.086678821593523e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.005491804797202349</v>
+        <v>0.0005776877515017986</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.03729970753192902</v>
+        <v>2.710250555537641e-06</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.004604061134159565</v>
+        <v>0.0004237511893734336</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.002529871882870793</v>
+        <v>1.081937807612121e-05</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.02214272320270538</v>
+        <v>3.865535836666822e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.008388334885239601</v>
+        <v>0.0004402979393489659</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1426878571510315</v>
+        <v>0.001996464096009731</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.04719049483537674</v>
+        <v>0.0004542226670309901</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.01429998129606247</v>
+        <v>0.0006370429182425141</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.02934888750314713</v>
+        <v>0.001145804300904274</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.03010068833827972</v>
+        <v>0.0007288899505510926</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.03113382682204247</v>
+        <v>2.612573734950274e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.003468126291409135</v>
+        <v>0.0007447990938089788</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.03165318816900253</v>
+        <v>0.0007660225383006036</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.003633022308349609</v>
+        <v>0.0003268892760388553</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.08171185851097107</v>
+        <v>2.199044683948159e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.05934037640690804</v>
+        <v>0.001059671863913536</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.01028682477772236</v>
+        <v>0.0006338272360153496</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.01920597068965435</v>
+        <v>0.0002820415247697383</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.02841269783675671</v>
+        <v>0.0004990471643395722</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.004741019569337368</v>
+        <v>5.298104952089489e-06</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.04038112610578537</v>
+        <v>0.001198794459924102</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.01817730627954006</v>
+        <v>0.0008269320242106915</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.01145474798977375</v>
+        <v>0.0001281784061575308</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.05375731363892555</v>
+        <v>0.0002312172728125006</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.03083842620253563</v>
+        <v>6.356494850479066e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.007127861492335796</v>
+        <v>0.0006587300449609756</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.004074492491781712</v>
+        <v>0.0001598238886799663</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.02435809373855591</v>
+        <v>0.0001100641311495565</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.02065270580351353</v>
+        <v>0.000147617349284701</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.000438361894339323</v>
+        <v>8.767715189605951e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.02419999055564404</v>
+        <v>0.0001212563220178708</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.006239723414182663</v>
+        <v>0.0001752702373778448</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.06856898218393326</v>
+        <v>0.001660701935179532</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0655546709895134</v>
+        <v>0.0001931650476763025</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.01524824649095535</v>
+        <v>9.02808242244646e-05</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.02743257768452168</v>
+        <v>0.0002439211239106953</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.01505301333963871</v>
+        <v>0.0007213125936686993</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.008079580031335354</v>
+        <v>0.0002543716400396079</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.002607285510748625</v>
+        <v>0.0003104660427197814</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.005113512743264437</v>
+        <v>0.00110322015825659</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.007299689576029778</v>
+        <v>9.818388207349926e-05</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.04740438237786293</v>
+        <v>0.001001360360532999</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.006305425427854061</v>
+        <v>0.0002568508207332343</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.005579016171395779</v>
+        <v>0.0008048743475228548</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.02200199104845524</v>
+        <v>7.099946378730237e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.004611825570464134</v>
+        <v>0.0003539007448125631</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.01186761632561684</v>
+        <v>0.0002020831452682614</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.01231157220900059</v>
+        <v>8.489044557791203e-05</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.005920770112425089</v>
+        <v>0.0003417022817302495</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.04296036809682846</v>
+        <v>0.0001317983696935698</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.02093463763594627</v>
+        <v>0.001108446856960654</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.01358634140342474</v>
+        <v>8.785481622908264e-05</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.01643460988998413</v>
+        <v>0.002221955452114344</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.01171394065022469</v>
+        <v>0.001037325244396925</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0602000430226326</v>
+        <v>0.001066816505044699</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0439043827354908</v>
+        <v>5.698857421521097e-05</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.01577568612992764</v>
+        <v>0.0002349531860090792</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.02827655151486397</v>
+        <v>0.0003321415861137211</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.006910395808517933</v>
+        <v>2.390716326772235e-05</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.04620373621582985</v>
+        <v>0.0009996804874390364</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.01199546176940203</v>
+        <v>0.0002084800653392449</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.01426183246076107</v>
+        <v>0.0008396446937695146</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.02974817529320717</v>
+        <v>6.678185309283435e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.006303736008703709</v>
+        <v>0.0005094229127280414</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0124198142439127</v>
+        <v>0.0002354402968194336</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.01627026870846748</v>
+        <v>0.0002848638978321105</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.001562827033922076</v>
+        <v>0.0006072008400224149</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.04725876450538635</v>
+        <v>3.406383621040732e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.05286617204546928</v>
+        <v>0.0004793980624526739</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.004033959470689297</v>
+        <v>0.0004867514362558722</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0543866753578186</v>
+        <v>0.0001610336184967309</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0405244268476963</v>
+        <v>0.001892807427793741</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.03829517215490341</v>
+        <v>0.001107339863665402</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.002220053225755692</v>
+        <v>0.0003091906837653369</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.02183861844241619</v>
+        <v>0.001628575613722205</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.03982254862785339</v>
+        <v>0.0007939883507788181</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.009611411020159721</v>
+        <v>0.0001526653650216758</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.02301420085132122</v>
+        <v>0.000177238107426092</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.009580580517649651</v>
+        <v>9.329240128863603e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0200444795191288</v>
+        <v>0.0004039315390400589</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.005784009117633104</v>
+        <v>0.0003725215792655945</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.01199579332023859</v>
+        <v>0.0001085237017832696</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.01340471394360065</v>
+        <v>0.0007771655800752342</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.02880650758743286</v>
+        <v>0.0006329413154162467</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.01998312026262283</v>
+        <v>0.0004395970026962459</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.004437556490302086</v>
+        <v>0.0003178687184117734</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.04455491155385971</v>
+        <v>0.0002962378493975848</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0210171602666378</v>
+        <v>0.0001358271110802889</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.001337788067758083</v>
+        <v>0.0006204155506566167</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.007796206511557102</v>
+        <v>0.0001416715094819665</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.0217187013477087</v>
+        <v>0.001104097347706556</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.007556492928415537</v>
+        <v>0.0006032528472132981</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.001133659388870001</v>
+        <v>0.0008864652481861413</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.01528788171708584</v>
+        <v>0.001251832349225879</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.02842530980706215</v>
+        <v>0.0002686892403289676</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.02787721529603004</v>
+        <v>0.0007812894182279706</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.01712825894355774</v>
+        <v>4.718007403425872e-06</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.006195398047566414</v>
+        <v>0.0006205789977684617</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.002327853813767433</v>
+        <v>4.89842495881021e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.009812943637371063</v>
+        <v>0.0002175553381675854</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.006100752390921116</v>
+        <v>0.0001347192737739533</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.0001756497658789158</v>
+        <v>2.962122380267829e-06</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.003945449367165565</v>
+        <v>0.0002039460523519665</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.0001301146112382412</v>
+        <v>0.0004182311822660267</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.03568445891141891</v>
+        <v>0.0009915408445522189</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.01225990056991577</v>
+        <v>2.117162694048602e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.01704124920070171</v>
+        <v>0.0004000315093435347</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.04034117609262466</v>
+        <v>0.0003644197131507099</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.01688701286911964</v>
+        <v>2.608166687423363e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.02981240674853325</v>
+        <v>0.0001202312269015238</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.03895566985011101</v>
+        <v>0.0001909692364279181</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.05012222006917</v>
+        <v>0.0001713686069706455</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.01342685520648956</v>
+        <v>3.528250817907974e-05</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.04536071047186852</v>
+        <v>0.00119753263425082</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.009124330244958401</v>
+        <v>0.0002140645665349439</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.006368489935994148</v>
+        <v>0.0008842034148983657</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02704738639295101</v>
+        <v>2.131107612513006e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.01009768713265657</v>
+        <v>0.0004820549511350691</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.01849189400672913</v>
+        <v>0.0001571891771163791</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.01623418368399143</v>
+        <v>0.0002946722670458257</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.01032263599336147</v>
+        <v>0.0005626571364700794</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.007750993594527245</v>
+        <v>0.0001071937003871426</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.01222531963139772</v>
+        <v>0.0004921084037050605</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.01782859861850739</v>
+        <v>0.0005610919906757772</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.01616217195987701</v>
+        <v>0.0003452630480751395</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.04057909548282623</v>
+        <v>0.0004556501808110625</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.007841167040169239</v>
+        <v>0.0001112945028580725</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.004511931445449591</v>
+        <v>0.0006150273256935179</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.02605859935283661</v>
+        <v>0.001062787720002234</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.02996622584760189</v>
+        <v>0.0004162645782344043</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.03092149458825588</v>
+        <v>0.0004163657722529024</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.008059829473495483</v>
+        <v>0.001012789434753358</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.05255837738513947</v>
+        <v>0.0003167265676893294</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.008367480710148811</v>
+        <v>0.001046515535563231</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01022344548255205</v>
+        <v>0.00101430295035243</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.02051020599901676</v>
+        <v>7.618451490998268e-06</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.01293567568063736</v>
+        <v>0.0001970562880160287</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.005414047744125128</v>
+        <v>0.0002488247118890285</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.01500506699085236</v>
+        <v>7.695233216509223e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.02673418633639812</v>
+        <v>0.0001508491550339386</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0244535319507122</v>
+        <v>0.0007968402933329344</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.03276589512825012</v>
+        <v>0.0002724325167946517</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0006672530435025692</v>
+        <v>0.0004141920071560889</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.002679275348782539</v>
+        <v>0.0008374305907636881</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.01628188788890839</v>
+        <v>0.001321773510426283</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0395660474896431</v>
+        <v>0.0005689286626875401</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.09976261854171753</v>
+        <v>0.0004840202745981514</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.02178124152123928</v>
+        <v>0.0005595447728410363</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.000907350389752537</v>
+        <v>0.003290480002760887</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01268154568970203</v>
+        <v>0.141123428940773</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0007322457386180758</v>
+        <v>0.0004507628036662936</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003431201912462711</v>
+        <v>0.05776182562112808</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001510578207671642</v>
+        <v>0.03680676966905594</v>
       </c>
       <c r="F17" t="n">
-        <v>0.008244827389717102</v>
+        <v>0.1518245041370392</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001664055860601366</v>
+        <v>0.03631100058555603</v>
       </c>
       <c r="H17" t="n">
-        <v>0.004313571378588676</v>
+        <v>0.09693513810634613</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0003180251223966479</v>
+        <v>0.01716886833310127</v>
       </c>
       <c r="J17" t="n">
-        <v>0.002207092009484768</v>
+        <v>0.01009798422455788</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01174016669392586</v>
+        <v>0.1979241073131561</v>
       </c>
       <c r="L17" t="n">
-        <v>0.000193328145542182</v>
+        <v>0.0318613313138485</v>
       </c>
       <c r="M17" t="n">
-        <v>0.002851213794201612</v>
+        <v>0.1257642060518265</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0007561584934592247</v>
+        <v>0.003971129655838013</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006532726809382439</v>
+        <v>0.2017428874969482</v>
       </c>
       <c r="P17" t="n">
-        <v>0.002566480077803135</v>
+        <v>0.005843351129442453</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.002228441881015897</v>
+        <v>0.01624388620257378</v>
       </c>
       <c r="R17" t="n">
-        <v>8.402322418987751e-05</v>
+        <v>0.05453179031610489</v>
       </c>
       <c r="S17" t="n">
-        <v>9.838283585850149e-05</v>
+        <v>0.01406653039157391</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0009660638170316815</v>
+        <v>0.04252107441425323</v>
       </c>
       <c r="U17" t="n">
-        <v>0.000270371267106384</v>
+        <v>0.003216336481273174</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0007180067477747798</v>
+        <v>0.04622988402843475</v>
       </c>
       <c r="W17" t="n">
-        <v>0.00126212986651808</v>
+        <v>0.01351368986070156</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0009820389095693827</v>
+        <v>0.01462535187602043</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0001089951547328383</v>
+        <v>0.02242928743362427</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.001024381257593632</v>
+        <v>0.0359705463051796</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0007396464934572577</v>
+        <v>0.01302520744502544</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0002037471276707947</v>
+        <v>0.02820008993148804</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0009387811296619475</v>
+        <v>0.0138298636302352</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0006007151678204536</v>
+        <v>0.002346776891499758</v>
       </c>
       <c r="AE17" t="n">
-        <v>8.703465573489666e-05</v>
+        <v>0.06535186618566513</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.00108433049172163</v>
+        <v>0.09902957081794739</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0004504704265855253</v>
+        <v>0.003975863102823496</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.176115908194333e-05</v>
+        <v>0.0002169366925954819</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0009275198681280017</v>
+        <v>0.1078341081738472</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0008514010114595294</v>
+        <v>0.02232770994305611</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.001309084007516503</v>
+        <v>0.01062251906841993</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.00151150964666158</v>
+        <v>0.03275604918599129</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0005663918564096093</v>
+        <v>4.422897472977638e-05</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0006480367155745625</v>
+        <v>0.015227185562253</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.001207529101520777</v>
+        <v>0.02446682006120682</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.002601188607513905</v>
+        <v>0.02515705861151218</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.000929299567360431</v>
+        <v>0.03007977269589901</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0009196283062919974</v>
+        <v>0.06237144395709038</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0008783219382166862</v>
+        <v>0.003749536816030741</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.0001428388059139252</v>
+        <v>0.01877466402947903</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.007330531720072031</v>
+        <v>0.2870701253414154</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.001992098987102509</v>
+        <v>0.01028412021696568</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0009276012424379587</v>
+        <v>0.04406880959868431</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.001253872876986861</v>
+        <v>0.02720854245126247</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.004980628378689289</v>
+        <v>0.1386539489030838</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.001629196107387543</v>
+        <v>0.003306131809949875</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.001922569470480084</v>
+        <v>0.01710437797009945</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.001222708146087825</v>
+        <v>0.01041416265070438</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0005587116465903819</v>
+        <v>0.005911595188081264</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.001967387739568949</v>
+        <v>0.08083761483430862</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.002332083415240049</v>
+        <v>0.005099969450384378</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.001848530955612659</v>
+        <v>0.0398838222026825</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.003351767314597964</v>
+        <v>0.03709247708320618</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.002783280331641436</v>
+        <v>0.02286626771092415</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0001026800455292687</v>
+        <v>0.01594594866037369</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0003924043849110603</v>
+        <v>0.0624476931989193</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0008569399360567331</v>
+        <v>0.003050995990633965</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0004480156640056521</v>
+        <v>0.02351075783371925</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.001082832110114396</v>
+        <v>0.0546576976776123</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0002430957974866033</v>
+        <v>0.0305359736084938</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0001236133684869856</v>
+        <v>0.005926739424467087</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.000309035851387307</v>
+        <v>0.01836122199892998</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0005600318545475602</v>
+        <v>0.0002216729335486889</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.001287967665120959</v>
+        <v>0.07340464740991592</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0005797009216621518</v>
+        <v>0.01646754518151283</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0002618745202198625</v>
+        <v>0.03115494176745415</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.0001126764691434801</v>
+        <v>0.001266916748136282</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.004339274019002914</v>
+        <v>0.1267572045326233</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0007182520930655301</v>
+        <v>0.01019955612719059</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.000535517290700227</v>
+        <v>0.02722820639610291</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.422916627954692e-05</v>
+        <v>0.01996007934212685</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.002382739912718534</v>
+        <v>0.07299993187189102</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0002045993751380593</v>
+        <v>0.04505838826298714</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0006742522236891091</v>
+        <v>0.01681458950042725</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0007697620894759893</v>
+        <v>0.02033632434904575</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.000311045499984175</v>
+        <v>0.01376457046717405</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.002237652195617557</v>
+        <v>0.05340762063860893</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0002989050117321312</v>
+        <v>0.0146580096334219</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0004559916560538113</v>
+        <v>0.01578907854855061</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0006630182033404708</v>
+        <v>0.002024848014116287</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0005411102902144194</v>
+        <v>0.03310767188668251</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0009993496350944042</v>
+        <v>0.01845451816916466</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0006296471692621708</v>
+        <v>0.006838308181613684</v>
       </c>
       <c r="CL17" t="n">
-        <v>3.490792005322874e-05</v>
+        <v>0.0001858739415183663</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.001920577138662338</v>
+        <v>0.04598703235387802</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.000150833380757831</v>
+        <v>0.1001042127609253</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0003768638707697392</v>
+        <v>0.04523920640349388</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.001928457757458091</v>
+        <v>0.08920552581548691</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0006776266964152455</v>
+        <v>0.02929830364882946</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.001447192626073956</v>
+        <v>0.01536146365106106</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.001319065107963979</v>
+        <v>0.002507869154214859</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0007694929372519255</v>
+        <v>0.001407189294695854</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0001742204185575247</v>
+        <v>0.000246663810685277</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0003174963349010795</v>
+        <v>0.0268065370619297</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.002193519845604897</v>
+        <v>0.04792720824480057</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0002998813288286328</v>
+        <v>0.01942890137434006</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0008555952226743102</v>
+        <v>0.02769107185304165</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0009214989258907735</v>
+        <v>0.01111630536615849</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0007143233087845147</v>
+        <v>0.04462094977498055</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.000866295478772372</v>
+        <v>0.004052006173878908</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.001243749749846756</v>
+        <v>0.001831361558288336</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.0001184482534881681</v>
+        <v>0.005535742733627558</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.001025611185468733</v>
+        <v>0.02041600272059441</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.003121317131444812</v>
+        <v>0.01737723127007484</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.0008600055589340627</v>
+        <v>0.02286718785762787</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.003108303062617779</v>
+        <v>0.006575598381459713</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.00463974243029952</v>
+        <v>0.05570270121097565</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.003132854355499148</v>
+        <v>0.01804842799901962</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0008251445251516998</v>
+        <v>0.04288448393344879</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.002843593945726752</v>
+        <v>0.01413963176310062</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.001470705610699952</v>
+        <v>0.05649661272764206</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0003131342527922243</v>
+        <v>0.01635205559432507</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0005775841418653727</v>
+        <v>0.004006263799965382</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0004121709789615124</v>
+        <v>0.01715283654630184</v>
       </c>
       <c r="DQ17" t="n">
-        <v>4.069741407874972e-05</v>
+        <v>0.04152931645512581</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0001669169869273901</v>
+        <v>0.0151709234341979</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.001368573284707963</v>
+        <v>0.04056927189230919</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0002416052739135921</v>
+        <v>0.02071043476462364</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.0001808419183362275</v>
+        <v>0.01008588075637817</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.0006266350974328816</v>
+        <v>0.03255387768149376</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0001593966298969463</v>
+        <v>0.01619850471615791</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.001133845071308315</v>
+        <v>0.03833095729351044</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0007781083695590496</v>
+        <v>0.0164266973733902</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0007085920660756528</v>
+        <v>0.00288054347038269</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.000451358500868082</v>
+        <v>0.01289799995720387</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.000835361541248858</v>
+        <v>0.00285894819535315</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.0006183597724884748</v>
+        <v>0.02509808540344238</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0009318147785961628</v>
+        <v>0.03717773407697678</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.001098297885619104</v>
+        <v>0.0719938725233078</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0009117292938753963</v>
+        <v>0.006952723022550344</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.002263124566525221</v>
+        <v>0.01607582159340382</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.0006651678122580051</v>
+        <v>0.01762570813298225</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.0004510232247412205</v>
+        <v>0.01165657304227352</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0002524036390241235</v>
+        <v>0.01586952805519104</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.0002912102499976754</v>
+        <v>0.008963317610323429</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0008906494476832449</v>
+        <v>0.0004759994335472584</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0002389359724475071</v>
+        <v>0.01529063656926155</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0002592047967482358</v>
+        <v>0.004827032331377268</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.000520318397320807</v>
+        <v>0.03155503794550896</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.002287334762513638</v>
+        <v>0.04577915370464325</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0006171435234136879</v>
+        <v>0.01904527470469475</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0009412061772309244</v>
+        <v>0.04012763872742653</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.001289759064093232</v>
+        <v>0.00773351825773716</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.0008482705452479422</v>
+        <v>0.007501367479562759</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.001037852140143514</v>
+        <v>0.01468182727694511</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.00160509895067662</v>
+        <v>0.03010673820972443</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0007555900956504047</v>
+        <v>0.007439335808157921</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.0005188659415580332</v>
+        <v>0.01850370317697525</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.002239650348201394</v>
+        <v>0.06222371384501457</v>
       </c>
       <c r="EZ17" t="n">
-        <v>1.743232132866979e-05</v>
+        <v>0.00682914350181818</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.000245267990976572</v>
+        <v>0.02623666636645794</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0008051072363741696</v>
+        <v>0.01623527333140373</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0005312031134963036</v>
+        <v>0.03565440326929092</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.001179489307105541</v>
+        <v>0.01997596584260464</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.001243575708940625</v>
+        <v>0.002323519205674529</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.00036618672311306</v>
+        <v>0.007923447526991367</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0006627911934629083</v>
+        <v>0.008762424811720848</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.0004267643671482801</v>
+        <v>0.01930616423487663</v>
       </c>
       <c r="FI17" t="n">
-        <v>2.124934690073133e-05</v>
+        <v>0.0008280258625745773</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.001413983525708318</v>
+        <v>0.03771987929940224</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0006030464428476989</v>
+        <v>0.02863926626741886</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.001382382237352431</v>
+        <v>0.06404396891593933</v>
       </c>
       <c r="FM17" t="n">
-        <v>7.104018004611135e-05</v>
+        <v>0.02351828664541245</v>
       </c>
       <c r="FN17" t="n">
-        <v>1.648563193157315e-05</v>
+        <v>0.01962187141180038</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0008101864950731397</v>
+        <v>0.07526402175426483</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.001444882829673588</v>
+        <v>0.01162587758153677</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0002008371957344934</v>
+        <v>0.01441880594938993</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.001556604402139783</v>
+        <v>0.05171893909573555</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0002729178522713482</v>
+        <v>0.01811109110713005</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.001760825631208718</v>
+        <v>0.06715662032365799</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0006803293363191187</v>
+        <v>0.02138594910502434</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0002741203061304986</v>
+        <v>0.005705768242478371</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001327659556409344</v>
+        <v>0.1035436913371086</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.001009470550343394</v>
+        <v>0.02959230728447437</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.001833660062402487</v>
+        <v>0.001948252320289612</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0007023223442956805</v>
+        <v>0.00618731090798974</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0009577304008416831</v>
+        <v>0.0327528715133667</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0004784695629496127</v>
+        <v>0.011818234808743</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.001821496756747365</v>
+        <v>0.05636446923017502</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.001523438608273864</v>
+        <v>0.01450648717582226</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.00153305206913501</v>
+        <v>0.05157880485057831</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0001507874694652855</v>
+        <v>0.02189764566719532</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0001318330760113895</v>
+        <v>0.002694775350391865</v>
       </c>
     </row>
     <row r="18">
